--- a/orgUnitMetaAttributeValueUpdate.xlsx
+++ b/orgUnitMetaAttributeValueUpdate.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\python_script_pirama_production\python_dhis2_integration\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{492D73EF-9BBE-4D1C-9F87-43E5D8B32EEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{505B9AE0-2666-42C0-96C7-B6D9BCA59096}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="807" uniqueCount="538">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="100">
   <si>
     <t>uid</t>
   </si>
@@ -44,1611 +44,295 @@
     <t>attributeValue</t>
   </si>
   <si>
-    <t>tQ7anLujM46</t>
+    <t>cVZvtezkCsM</t>
   </si>
   <si>
-    <t>zTJUQVd0boO</t>
+    <t>NMZDc62VkUu</t>
   </si>
   <si>
-    <t>SvnzJYdzIWQ</t>
+    <t>YoKkWEKk8Vs</t>
   </si>
   <si>
-    <t>Ot1M0X6Umms</t>
+    <t>eEJjlb96A9S</t>
   </si>
   <si>
-    <t>WnBPJQz4l4c</t>
+    <t>GR1K45ToRLP</t>
   </si>
   <si>
-    <t>aW6LXQ7hXTn</t>
+    <t>gyF1IWxbNdU</t>
   </si>
   <si>
-    <t>X1VD21QsmyQ</t>
+    <t>sp7Kp98AgiY</t>
   </si>
   <si>
-    <t>EaWRGK0juDM</t>
+    <t>WLBxL2ClHIC</t>
   </si>
   <si>
-    <t>aleWZ0snpbF</t>
+    <t>ZWwcPbXbh7A</t>
   </si>
   <si>
-    <t>ZZdZevkav5L</t>
+    <t>M0h4xQCnr5Q</t>
   </si>
   <si>
-    <t>PvtASqM2ixJ</t>
+    <t>X1XpOXDu4i1</t>
   </si>
   <si>
-    <t>LHaNEMTVSLR</t>
+    <t>Bqbp4RSh59F</t>
   </si>
   <si>
-    <t>LzuWI4sMTNL</t>
+    <t>RiNRNy2QrbG</t>
   </si>
   <si>
-    <t>Z3O0uqD17Uu</t>
+    <t>NbSwp2REKl2</t>
   </si>
   <si>
-    <t>PHbj88YLRbJ</t>
+    <t>bZ0QNxepVDm</t>
   </si>
   <si>
-    <t>EfulAdgBPI9</t>
+    <t>l45fr3dt5Hj</t>
   </si>
   <si>
-    <t>gvW0b4xBwcU</t>
+    <t>as6EmlRFNGM</t>
   </si>
   <si>
-    <t>SZSri2Z4JG3</t>
+    <t>PJdV5nECQnS</t>
   </si>
   <si>
-    <t>U8IdsrV8p2x</t>
+    <t>Hip7Iiwe0Zw</t>
   </si>
   <si>
-    <t>PHIdPwMMRfa</t>
+    <t>AgTsGtf7kdS</t>
   </si>
   <si>
-    <t>mIJ0Ch8qJwE</t>
+    <t>EoD53fBetjK</t>
   </si>
   <si>
-    <t>EniFJNW3Y47</t>
+    <t>vNpX4nuwSQ4</t>
   </si>
   <si>
-    <t>HkPeiwQJXGY</t>
+    <t>z4jth5bBeTQ</t>
   </si>
   <si>
-    <t>qyi4GP1jcE6</t>
+    <t>uhP4XuZMhmP</t>
   </si>
   <si>
-    <t>oGI3XzRkINz</t>
+    <t>kenJxBny3sm</t>
   </si>
   <si>
-    <t>c0KSZZIXuuj</t>
+    <t>aXquUzlrYYv</t>
   </si>
   <si>
-    <t>PLPKCtzXzwD</t>
+    <t>Put4ZMYsdZf</t>
   </si>
   <si>
-    <t>A00qT2rlsEz</t>
+    <t>WaY0NFhl8Y3</t>
   </si>
   <si>
-    <t>n4Mrrm8ZwD0</t>
+    <t>Eps9XCDyPWJ</t>
   </si>
   <si>
-    <t>uqmXErxldnG</t>
+    <t>FfqjUkvHaq2</t>
   </si>
   <si>
-    <t>IJMJ5djid6H</t>
+    <t>fZcTJkUmgnD</t>
   </si>
   <si>
-    <t>OlFS49aYNOt</t>
+    <t>OZGBcyvt0Eq</t>
   </si>
   <si>
-    <t>abYGDxDmVel</t>
+    <t>t0fTpHGj4pA</t>
   </si>
   <si>
-    <t>sPZb1ZocjgM</t>
+    <t>LMiy1iX4Lnr</t>
   </si>
   <si>
-    <t>PeOGgXf0puh</t>
+    <t>aUv4lHwAFh9</t>
   </si>
   <si>
-    <t>C1EZtIOnPlf</t>
+    <t>J6GqvSHE3ql</t>
   </si>
   <si>
-    <t>owqn0pbVNMb</t>
+    <t>popAWkAUmV7</t>
   </si>
   <si>
-    <t>BaxJwMMO7fr</t>
+    <t>pLGBXoHij8l</t>
   </si>
   <si>
-    <t>bTBPsDEgbKX</t>
+    <t>sTpP9XtNNIq</t>
   </si>
   <si>
-    <t>AkMkoK4abuS</t>
+    <t>E7KRzq0nI80</t>
   </si>
   <si>
-    <t>s0kigUXqDa3</t>
+    <t>TXvMmNVpTbV</t>
   </si>
   <si>
-    <t>WmF2zZavMiL</t>
+    <t>PPy8McaEWmP</t>
   </si>
   <si>
-    <t>ZYRAEDM1saQ</t>
+    <t>vZ2BOsyGD6k</t>
   </si>
   <si>
-    <t>z95AY1nk9hD</t>
+    <t>hOBq8ofsGIA</t>
   </si>
   <si>
-    <t>ZmICGIPcnrK</t>
+    <t>yIw4RH3Pdwi</t>
   </si>
   <si>
-    <t>jigEniEH6jU</t>
+    <t>SlJVRDSnSs7</t>
   </si>
   <si>
-    <t>cz29wre2TNG</t>
+    <t>e8msu3rYPr7</t>
   </si>
   <si>
-    <t>UndpMJDFVIY</t>
+    <t>mL4Cbzwq1T7</t>
   </si>
   <si>
-    <t>uLRlqiDiF8V</t>
+    <t>HII00nHXHSr</t>
   </si>
   <si>
-    <t>L0WoJ3YwqSR</t>
+    <t>FSMALlcEMN1</t>
   </si>
   <si>
-    <t>nvj4nh9v3Rz</t>
+    <t>mIZ7UfitSfF</t>
   </si>
   <si>
-    <t>WitvNTHI1do</t>
+    <t>k2gEfAppdDa</t>
   </si>
   <si>
-    <t>VwiowOC62sk</t>
+    <t>bJprtQeaalg</t>
   </si>
   <si>
-    <t>hed7eUsM4hp</t>
+    <t>vcjdAdENK6U</t>
   </si>
   <si>
-    <t>kUtsirVG9t2</t>
+    <t>mkjer41pShd</t>
   </si>
   <si>
-    <t>n05t23ZB6LX</t>
+    <t>enCNn7DBvEe</t>
   </si>
   <si>
-    <t>GwpffQRPVwS</t>
+    <t>kgYQV9tV9Ep</t>
   </si>
   <si>
-    <t>tNZdTN6j03P</t>
+    <t>RkDkH6DBxHZ</t>
   </si>
   <si>
-    <t>HuCIrjN2atR</t>
+    <t>mrjraHkF3r7</t>
   </si>
   <si>
-    <t>m4DXsYO7i3b</t>
+    <t>i4idGldWCti</t>
   </si>
   <si>
-    <t>x11v5Un6V9O</t>
+    <t>TG9xwiyOzFy</t>
   </si>
   <si>
-    <t>J13BfCamdj8</t>
+    <t>YiaQ5cJ9SKf</t>
   </si>
   <si>
-    <t>YEk4VexOg9G</t>
+    <t>mPO6LgjseUd</t>
   </si>
   <si>
-    <t>QNobr3GG4aW</t>
+    <t>Cnl0ZbkVdCp</t>
   </si>
   <si>
-    <t>Zxe9SKe1LvV</t>
+    <t>gmBf8LmHER8</t>
   </si>
   <si>
-    <t>ydIYbvd7enK</t>
+    <t>oh55nKvLTZ3</t>
   </si>
   <si>
-    <t>VX014Nrq30T</t>
+    <t>PaPESMnNmGS</t>
   </si>
   <si>
-    <t>ouNFyPbFcAW</t>
+    <t>HSlfDph63Nq</t>
   </si>
   <si>
-    <t>BFSggRprfPH</t>
+    <t>cLAmxlnT75s</t>
   </si>
   <si>
-    <t>M4URaBQJUa5</t>
+    <t>Bm39oMfSNir</t>
   </si>
   <si>
-    <t>EaHH97UU4HZ</t>
+    <t>YZEW9zco5wp</t>
   </si>
   <si>
-    <t>nH7PxOvLevy</t>
+    <t>wW6BjmcZPTE</t>
   </si>
   <si>
-    <t>zEk8MIuA5yq</t>
+    <t>VHupBnQcURm</t>
   </si>
   <si>
-    <t>px4XwruWBtE</t>
+    <t>xQ9yCoUNMvb</t>
   </si>
   <si>
-    <t>enhtOJV0dF1</t>
+    <t>dz76561Tykq</t>
   </si>
   <si>
-    <t>iVfju9pUvZs</t>
+    <t>gYWUCbDn7W9</t>
   </si>
   <si>
-    <t>hrqvQYvEId3</t>
+    <t>CZSqk9wH36L</t>
   </si>
   <si>
-    <t>LQvpES0ICUm</t>
+    <t>BiBfVGxLkLE</t>
   </si>
   <si>
-    <t>bpYsH47E4mU</t>
+    <t>iAqA94CYN5T</t>
   </si>
   <si>
-    <t>W8A4NLSGD1y</t>
+    <t>ICouwFuLi6e</t>
   </si>
   <si>
-    <t>G1Z1cc2s7Iu</t>
+    <t>Jyk5lg7lSJE</t>
   </si>
   <si>
-    <t>uNrL9713qXx</t>
+    <t>qf1SFbsoO5U</t>
   </si>
   <si>
-    <t>a3eKEw5cKl2</t>
+    <t>DEV82n2a57B</t>
   </si>
   <si>
-    <t>lVAijzN3ZCI</t>
+    <t>V4Mdjx4dLU6</t>
   </si>
   <si>
-    <t>jBksvpll8Pp</t>
+    <t>UcFtqIBF6dF</t>
   </si>
   <si>
-    <t>kQfI2pHwzha</t>
+    <t>k7nVtjJsFcc</t>
   </si>
   <si>
-    <t>g54atKCWYm2</t>
+    <t>nEIktLQW451</t>
   </si>
   <si>
-    <t>CfDRI0dTOWB</t>
+    <t>pKR0mkabc8U</t>
   </si>
   <si>
-    <t>Hf7NSNTQX9l</t>
+    <t>nPv9ZSw7DU3</t>
   </si>
   <si>
-    <t>ZAwYgBGTDbc</t>
+    <t>DYcRiFnkTeh</t>
   </si>
   <si>
-    <t>tMWQTtRZqCt</t>
+    <t>igUB7D4ujIp</t>
   </si>
   <si>
-    <t>pq1mCuq2kSi</t>
+    <t>StYGSnQkGYd</t>
   </si>
   <si>
-    <t>Svmy1zWfcGL</t>
+    <t>UPxxC2e48GJ</t>
   </si>
   <si>
-    <t>kTRdce71DMX</t>
+    <t>u11K0KqXoo4</t>
   </si>
   <si>
-    <t>prHbrcBfgvH</t>
+    <t>kDfTb2xmcJq</t>
   </si>
   <si>
-    <t>nOaFT04IrGt</t>
+    <t>EySK9sIwopW</t>
   </si>
   <si>
-    <t>s5seAimR7td</t>
-  </si>
-  <si>
-    <t>nxVVU0EVt3H</t>
-  </si>
-  <si>
-    <t>ggHtPugzahM</t>
-  </si>
-  <si>
-    <t>EGFe4tamLc8</t>
-  </si>
-  <si>
-    <t>NdDsu0jBWwm</t>
-  </si>
-  <si>
-    <t>V2F7MAAFSyY</t>
-  </si>
-  <si>
-    <t>EDbFPVZsS0S</t>
-  </si>
-  <si>
-    <t>hueahaiL5U7</t>
-  </si>
-  <si>
-    <t>c6SR0Q5cr0f</t>
-  </si>
-  <si>
-    <t>fmbxdY8CFVA</t>
-  </si>
-  <si>
-    <t>JUqLtrK3LTZ</t>
-  </si>
-  <si>
-    <t>RbKiQpySrz9</t>
-  </si>
-  <si>
-    <t>YNJL1kowkOr</t>
-  </si>
-  <si>
-    <t>fWRi0emdSok</t>
-  </si>
-  <si>
-    <t>K2Xv4Sy5cPb</t>
-  </si>
-  <si>
-    <t>SEna7mDYGB4</t>
-  </si>
-  <si>
-    <t>uyXpRWFzAVG</t>
-  </si>
-  <si>
-    <t>vrqXis1tvq5</t>
-  </si>
-  <si>
-    <t>oCfa0rHRI27</t>
-  </si>
-  <si>
-    <t>IESRNgGwj4o</t>
-  </si>
-  <si>
-    <t>vi2yTwX51gk</t>
-  </si>
-  <si>
-    <t>PXBIpqclGsK</t>
-  </si>
-  <si>
-    <t>pBaWwBlH0CT</t>
-  </si>
-  <si>
-    <t>aaLhwV2tgrY</t>
-  </si>
-  <si>
-    <t>e99YHijgHk6</t>
-  </si>
-  <si>
-    <t>rqrbAoqFgzJ</t>
-  </si>
-  <si>
-    <t>UlpCG1PXteZ</t>
-  </si>
-  <si>
-    <t>TPabVNUPMJj</t>
-  </si>
-  <si>
-    <t>Gz2MigUleP3</t>
-  </si>
-  <si>
-    <t>ajPMDbtwAnv</t>
-  </si>
-  <si>
-    <t>xGr27twuruv</t>
-  </si>
-  <si>
-    <t>acyeMnx4sKK</t>
-  </si>
-  <si>
-    <t>SqYxsh0XpJ9</t>
-  </si>
-  <si>
-    <t>JeLZ9FmfBCI</t>
-  </si>
-  <si>
-    <t>aK7fhgpv7fO</t>
-  </si>
-  <si>
-    <t>qBM40wptLv0</t>
-  </si>
-  <si>
-    <t>qYdWgdfGAmr</t>
-  </si>
-  <si>
-    <t>QvUnX6LWoo1</t>
-  </si>
-  <si>
-    <t>eAzcI11N8jA</t>
-  </si>
-  <si>
-    <t>rk5HSAVqvlG</t>
-  </si>
-  <si>
-    <t>XD6VaZ0DIT5</t>
-  </si>
-  <si>
-    <t>GfZ4XXkmyYV</t>
-  </si>
-  <si>
-    <t>zvTl1OtBeev</t>
-  </si>
-  <si>
-    <t>RlwwIOwmSK8</t>
-  </si>
-  <si>
-    <t>r14ztL6bX4Z</t>
-  </si>
-  <si>
-    <t>zv4Ibs25IKp</t>
-  </si>
-  <si>
-    <t>npJFVndsdyr</t>
-  </si>
-  <si>
-    <t>Lk365Ex0iAY</t>
-  </si>
-  <si>
-    <t>jzlqLaiCYeK</t>
-  </si>
-  <si>
-    <t>ZZEsdFXbMBS</t>
-  </si>
-  <si>
-    <t>jZnW4m6KbnV</t>
-  </si>
-  <si>
-    <t>O7h76oh3pre</t>
-  </si>
-  <si>
-    <t>xLsVDfOX1ZM</t>
-  </si>
-  <si>
-    <t>A9fV1SQenX7</t>
-  </si>
-  <si>
-    <t>g09S1jVBasi</t>
-  </si>
-  <si>
-    <t>AnAZjEXbEAT</t>
-  </si>
-  <si>
-    <t>oB61p3phcRY</t>
-  </si>
-  <si>
-    <t>qH0jReMeMmV</t>
-  </si>
-  <si>
-    <t>sd37ImWf0mr</t>
-  </si>
-  <si>
-    <t>gTGngsqOYsH</t>
-  </si>
-  <si>
-    <t>lEReUiM2IPl</t>
-  </si>
-  <si>
-    <t>HLGq7LfUGuo</t>
-  </si>
-  <si>
-    <t>DdyUMwdjOgx</t>
-  </si>
-  <si>
-    <t>MrkwndNOWe1</t>
-  </si>
-  <si>
-    <t>aQLmcwqno7U</t>
-  </si>
-  <si>
-    <t>CUhFWKNpzTi</t>
-  </si>
-  <si>
-    <t>jmtj2NWyvKI</t>
-  </si>
-  <si>
-    <t>ycUxqKEh71r</t>
-  </si>
-  <si>
-    <t>TmprfzPNJs4</t>
-  </si>
-  <si>
-    <t>gKt79dNlTWk</t>
-  </si>
-  <si>
-    <t>Y9EvlDMmJ4D</t>
-  </si>
-  <si>
-    <t>fJeT9rB8NjD</t>
-  </si>
-  <si>
-    <t>PWyyYgGgzPK</t>
-  </si>
-  <si>
-    <t>Ig0tR8GmXGH</t>
-  </si>
-  <si>
-    <t>ilm1WLIw6Ai</t>
-  </si>
-  <si>
-    <t>mibNJQCdTs8</t>
-  </si>
-  <si>
-    <t>unmN1HYV9r3</t>
-  </si>
-  <si>
-    <t>Qj6Xe3meg4T</t>
-  </si>
-  <si>
-    <t>cEgMtJnGkNZ</t>
-  </si>
-  <si>
-    <t>I1GyJcDm0Zb</t>
-  </si>
-  <si>
-    <t>uEORr899xlL</t>
-  </si>
-  <si>
-    <t>TZPEuwYA8mf</t>
-  </si>
-  <si>
-    <t>U5ME5NpQL6K</t>
-  </si>
-  <si>
-    <t>twAu1ou7Ebu</t>
-  </si>
-  <si>
-    <t>fCjmsl3svhM</t>
-  </si>
-  <si>
-    <t>rIEyoV2wNyO</t>
-  </si>
-  <si>
-    <t>BWkLM1At9m9</t>
-  </si>
-  <si>
-    <t>XV9DiprKr3v</t>
-  </si>
-  <si>
-    <t>xWG4cYUHcCl</t>
-  </si>
-  <si>
-    <t>cbPvxWt38iy</t>
-  </si>
-  <si>
-    <t>poyoqLur1eb</t>
-  </si>
-  <si>
-    <t>IvzQxQP6wU0</t>
-  </si>
-  <si>
-    <t>BDdRWkFf7fO</t>
-  </si>
-  <si>
-    <t>X518jDQ0AeD</t>
-  </si>
-  <si>
-    <t>lCErbHS5bfm</t>
-  </si>
-  <si>
-    <t>FSaHLH8uGEi</t>
-  </si>
-  <si>
-    <t>ZJgYfdSoZJP</t>
-  </si>
-  <si>
-    <t>Q0F2GvKQHAJ</t>
-  </si>
-  <si>
-    <t>IHEDhqKyP9X</t>
-  </si>
-  <si>
-    <t>HFTFlHYFcki</t>
-  </si>
-  <si>
-    <t>dCk5cBlN5wG</t>
-  </si>
-  <si>
-    <t>DeM0suOhO39</t>
-  </si>
-  <si>
-    <t>Kp6MvPRmzFx</t>
-  </si>
-  <si>
-    <t>BCJiOl6SSky</t>
-  </si>
-  <si>
-    <t>hc4wL307jch</t>
-  </si>
-  <si>
-    <t>oKtiRp8yHYH</t>
-  </si>
-  <si>
-    <t>orEchzplHfQ</t>
-  </si>
-  <si>
-    <t>Lme0mGfrIKS</t>
-  </si>
-  <si>
-    <t>hNyIloa4k9Y</t>
-  </si>
-  <si>
-    <t>MtzWsFKKfET</t>
-  </si>
-  <si>
-    <t>nWJgk1VKT1e</t>
-  </si>
-  <si>
-    <t>l2rayuYsD8q</t>
-  </si>
-  <si>
-    <t>zbTEa7Nq0Hk</t>
-  </si>
-  <si>
-    <t>CEDOmRWz735</t>
-  </si>
-  <si>
-    <t>YmpziDWzX2J</t>
-  </si>
-  <si>
-    <t>XhrXcVNROvA</t>
-  </si>
-  <si>
-    <t>AvGe8VJunmo</t>
-  </si>
-  <si>
-    <t>HVfNQptEo5E</t>
-  </si>
-  <si>
-    <t>NoDxYREboCx</t>
-  </si>
-  <si>
-    <t>F99JwwxCaQY</t>
-  </si>
-  <si>
-    <t>YgRIM4r6FJu</t>
-  </si>
-  <si>
-    <t>bbca8q5qHAp</t>
-  </si>
-  <si>
-    <t>Ty8YuZVvtat</t>
-  </si>
-  <si>
-    <t>wVKxukW9f5d</t>
-  </si>
-  <si>
-    <t>WVcSxeOu2ur</t>
-  </si>
-  <si>
-    <t>mw2liC9H5vN</t>
-  </si>
-  <si>
-    <t>XTi3iGvvETu</t>
-  </si>
-  <si>
-    <t>CDD6uSWL1cc</t>
-  </si>
-  <si>
-    <t>xiwmIVXwkuo</t>
-  </si>
-  <si>
-    <t>GvCQZ7i2F2h</t>
-  </si>
-  <si>
-    <t>JYkd06kuKY2</t>
-  </si>
-  <si>
-    <t>AL8wROh8T3y</t>
-  </si>
-  <si>
-    <t>Pxx9BxzVhMY</t>
-  </si>
-  <si>
-    <t>iaHNm7jX4iv</t>
-  </si>
-  <si>
-    <t>vQsLmA8tPG3</t>
-  </si>
-  <si>
-    <t>qJYyaelz3DD</t>
-  </si>
-  <si>
-    <t>YFry15xAm6L</t>
-  </si>
-  <si>
-    <t>BCYOL7fQZKk</t>
-  </si>
-  <si>
-    <t>qEdJst6Tfgb</t>
-  </si>
-  <si>
-    <t>sdY1a1SEWev</t>
-  </si>
-  <si>
-    <t>BySTYmYNbke</t>
-  </si>
-  <si>
-    <t>aTEOM1VyiD0</t>
-  </si>
-  <si>
-    <t>l3LvW6Ay5Vn</t>
-  </si>
-  <si>
-    <t>L1Y8tJmPsD0</t>
-  </si>
-  <si>
-    <t>fwv8WGX8jqT</t>
-  </si>
-  <si>
-    <t>bmF7SbhGM66</t>
-  </si>
-  <si>
-    <t>TrM7uLgSXH8</t>
-  </si>
-  <si>
-    <t>cxcWS8hEBLX</t>
-  </si>
-  <si>
-    <t>KXMTCxuyrLJ</t>
-  </si>
-  <si>
-    <t>Okrkm1jeije</t>
-  </si>
-  <si>
-    <t>Uw0L0W4xHR4</t>
-  </si>
-  <si>
-    <t>ZtvtX5OCogy</t>
-  </si>
-  <si>
-    <t>k9wggPs48nc</t>
-  </si>
-  <si>
-    <t>DCEtWTgDKFa</t>
-  </si>
-  <si>
-    <t>y7bcgTKTaVP</t>
-  </si>
-  <si>
-    <t>y0U6zqProfM</t>
-  </si>
-  <si>
-    <t>plVBmLwN2y1</t>
-  </si>
-  <si>
-    <t>VVJmyLkxv63</t>
-  </si>
-  <si>
-    <t>a0MAs8TSmya</t>
-  </si>
-  <si>
-    <t>D1hqtfk1EjC</t>
-  </si>
-  <si>
-    <t>qIB5rwe2OLM</t>
-  </si>
-  <si>
-    <t>ezwQt0GXHHr</t>
-  </si>
-  <si>
-    <t>m0CGaEZ2RRM</t>
-  </si>
-  <si>
-    <t>sWZrS2oliwf</t>
-  </si>
-  <si>
-    <t>vv6wn5CM7EG</t>
-  </si>
-  <si>
-    <t>wzo0LtfBfGk</t>
-  </si>
-  <si>
-    <t>QE0WaXGV58z</t>
-  </si>
-  <si>
-    <t>IssoQw6moFJ</t>
-  </si>
-  <si>
-    <t>hsGMfHFr7rg</t>
-  </si>
-  <si>
-    <t>rhvz4osW1wn</t>
-  </si>
-  <si>
-    <t>JVueUmEGlY4</t>
-  </si>
-  <si>
-    <t>HvVFD2eC6SF</t>
-  </si>
-  <si>
-    <t>J5sfkpphrKm</t>
-  </si>
-  <si>
-    <t>IPPF-AUT-002</t>
-  </si>
-  <si>
-    <t>IPPF-LBN-004</t>
-  </si>
-  <si>
-    <t>IPPF-CAN-001</t>
-  </si>
-  <si>
-    <t>IPPF-NPL-001</t>
-  </si>
-  <si>
-    <t>IPPF-AFG-001</t>
-  </si>
-  <si>
-    <t>IPPF-JOR-001</t>
-  </si>
-  <si>
-    <t>IPPF-SYC-001</t>
-  </si>
-  <si>
-    <t>IPPF-AIA-001</t>
-  </si>
-  <si>
-    <t>IPPF-ATG-001</t>
-  </si>
-  <si>
-    <t>IPPF-ARM-001</t>
-  </si>
-  <si>
-    <t>IPPF-CHL-001</t>
-  </si>
-  <si>
-    <t>IPPF-PRY-001</t>
-  </si>
-  <si>
-    <t>IPPF-CRI-001</t>
-  </si>
-  <si>
-    <t>IPPF-SLV-002</t>
-  </si>
-  <si>
-    <t>IPPF-DOM-001</t>
-  </si>
-  <si>
-    <t>IPPF-HND-001</t>
-  </si>
-  <si>
-    <t>IPPF-GTM-001</t>
-  </si>
-  <si>
-    <t>IPPF-PAN-001</t>
-  </si>
-  <si>
-    <t>IPPF-COL-001</t>
-  </si>
-  <si>
-    <t>IPPF-GTM-003</t>
-  </si>
-  <si>
-    <t>IPPF-NIC-002</t>
-  </si>
-  <si>
-    <t>IPPF-PRI-001</t>
-  </si>
-  <si>
-    <t>IPPF-URY-002</t>
-  </si>
-  <si>
-    <t>IPPF-VEN-002</t>
-  </si>
-  <si>
-    <t>IPPF-PER-001</t>
-  </si>
-  <si>
-    <t>IPPF-AGO-001</t>
-  </si>
-  <si>
-    <t>IPPF-CPV-001</t>
-  </si>
-  <si>
-    <t>IPPF-GNB-001</t>
-  </si>
-  <si>
-    <t>IPPF-MOZ-001</t>
-  </si>
-  <si>
-    <t>IPPF-PRT-001</t>
-  </si>
-  <si>
-    <t>IPPF-STP-001</t>
-  </si>
-  <si>
-    <t>IPPF-DZA-001</t>
-  </si>
-  <si>
-    <t>IPPF-BEN-001</t>
-  </si>
-  <si>
-    <t>IPPF-GNQ-001</t>
-  </si>
-  <si>
-    <t>IPPF-BFA-002</t>
-  </si>
-  <si>
-    <t>IPPF-BDI-001</t>
-  </si>
-  <si>
-    <t>IPPF-CAF-001</t>
-  </si>
-  <si>
-    <t>IPPF-COM-001</t>
-  </si>
-  <si>
-    <t>IPPF-COG-001</t>
-  </si>
-  <si>
-    <t>IPPF-HTI-001</t>
-  </si>
-  <si>
-    <t>IPPF-DJI-001</t>
-  </si>
-  <si>
-    <t>IPPF-HRV-001</t>
-  </si>
-  <si>
-    <t>IPPF-BGD-001</t>
-  </si>
-  <si>
-    <t>IPPF-GLP-001</t>
-  </si>
-  <si>
-    <t>IPPF-GIN-003</t>
-  </si>
-  <si>
-    <t>IPPF-GEO-001</t>
-  </si>
-  <si>
-    <t>IPPF-CIV-004</t>
-  </si>
-  <si>
-    <t>IPPF-MLI-001</t>
-  </si>
-  <si>
-    <t>IPPF-MAR-001</t>
-  </si>
-  <si>
-    <t>IPPF-MTQ-001</t>
-  </si>
-  <si>
-    <t>IPPF-MRT-001</t>
-  </si>
-  <si>
-    <t>IPPF-NER-001</t>
-  </si>
-  <si>
-    <t>IPPF-UGA-002</t>
-  </si>
-  <si>
-    <t>IPPF-TUR-005</t>
-  </si>
-  <si>
-    <t>IPPF-HTI-003</t>
-  </si>
-  <si>
-    <t>IPPF-COD-002</t>
-  </si>
-  <si>
-    <t>IPPF-RWA-002</t>
-  </si>
-  <si>
-    <t>IPPF-SEN-001</t>
-  </si>
-  <si>
-    <t>IPPF-SEN-003</t>
-  </si>
-  <si>
-    <t>IPPF-TCD-001</t>
-  </si>
-  <si>
-    <t>IPPF-TGO-002</t>
-  </si>
-  <si>
-    <t>IPPF-BHS-001</t>
-  </si>
-  <si>
-    <t>IPPF-BHR-001</t>
-  </si>
-  <si>
-    <t>IPPF-BGD-002</t>
-  </si>
-  <si>
-    <t>IPPF-BGD-003</t>
-  </si>
-  <si>
-    <t>IPPF-BLR-001</t>
-  </si>
-  <si>
-    <t>IPPF-BLZ-001</t>
-  </si>
-  <si>
-    <t>IPPF-BRA-006</t>
-  </si>
-  <si>
-    <t>IPPF-BWA-001</t>
-  </si>
-  <si>
-    <t>IPPF-GBR-003</t>
-  </si>
-  <si>
-    <t>IPPF-BGR-001</t>
-  </si>
-  <si>
-    <t>IPPF-CMR-001</t>
-  </si>
-  <si>
-    <t>IPPF-CAN-003</t>
-  </si>
-  <si>
-    <t>IPPF-ECU-003</t>
-  </si>
-  <si>
-    <t>IPPF-SRB-002</t>
-  </si>
-  <si>
-    <t>IPPF-USA-010</t>
-  </si>
-  <si>
-    <t>IPPF-BOL-002</t>
-  </si>
-  <si>
-    <t>IPPF-ECU-002</t>
-  </si>
-  <si>
-    <t>IPPF-MOZ-002</t>
-  </si>
-  <si>
-    <t>IPPF-CHN-001</t>
-  </si>
-  <si>
-    <t>IPF-BRA-007</t>
-  </si>
-  <si>
-    <t>IPPF-BOL-003</t>
-  </si>
-  <si>
-    <t>IPPF-COD-008</t>
-  </si>
-  <si>
-    <t>IPPF-FRA-008</t>
-  </si>
-  <si>
-    <t>IPPF-LBR-001</t>
-  </si>
-  <si>
-    <t>IPPF-PER-002</t>
-  </si>
-  <si>
-    <t>IPPF-COK-001</t>
-  </si>
-  <si>
-    <t>IPPF-ZMB-001</t>
-  </si>
-  <si>
-    <t>IPPF-CYP-001</t>
-  </si>
-  <si>
-    <t>IPPF-DMA-002</t>
-  </si>
-  <si>
-    <t>IPPF-EST-002</t>
-  </si>
-  <si>
-    <t>IPPF-EGY-001</t>
-  </si>
-  <si>
-    <t>IPPF-CUB-001</t>
-  </si>
-  <si>
-    <t>IPPF-PRY-002</t>
-  </si>
-  <si>
-    <t>IPPF-HUN-003</t>
-  </si>
-  <si>
-    <t>IPPF-TUN-001</t>
-  </si>
-  <si>
-    <t>IPPF-ECU-006</t>
-  </si>
-  <si>
-    <t>IPPF-BEL-004</t>
-  </si>
-  <si>
-    <t>IPPF-ETH-007</t>
-  </si>
-  <si>
-    <t>IPPF-IRN-001</t>
-  </si>
-  <si>
-    <t>IPPF-ARM-002</t>
-  </si>
-  <si>
-    <t>IPPF-KEN-006</t>
-  </si>
-  <si>
-    <t>IPPF-SWZ-001</t>
-  </si>
-  <si>
-    <t>IPPF-AUS-001</t>
-  </si>
-  <si>
-    <t>IPPF-TWN-001</t>
-  </si>
-  <si>
-    <t>IPPF-BGD-004</t>
-  </si>
-  <si>
-    <t>IPPF-GRC-001</t>
-  </si>
-  <si>
-    <t>IPPF-HKG-001</t>
-  </si>
-  <si>
-    <t>IPPF-IND-001</t>
-  </si>
-  <si>
-    <t>IPPF-MWI-002</t>
-  </si>
-  <si>
-    <t>IPPF-NPL-002</t>
-  </si>
-  <si>
-    <t>IPPF-LKA-002</t>
-  </si>
-  <si>
-    <t>IPPF-TTO-002</t>
-  </si>
-  <si>
-    <t>IPPF-PHL-002</t>
-  </si>
-  <si>
-    <t>IPPF-ERI-001</t>
-  </si>
-  <si>
-    <t>IPPF-POL-001</t>
-  </si>
-  <si>
-    <t>IPPF-ESP-001</t>
-  </si>
-  <si>
-    <t>IPPF-MYS-001</t>
-  </si>
-  <si>
-    <t>IPPF-PRK-001</t>
-  </si>
-  <si>
-    <t>IPPF-MDG-002</t>
-  </si>
-  <si>
-    <t>IPPF-UGA-004</t>
-  </si>
-  <si>
-    <t>IPPF-ECU-007</t>
-  </si>
-  <si>
-    <t>IPPF-CUW-001</t>
-  </si>
-  <si>
-    <t>IPPF-ABW-001</t>
-  </si>
-  <si>
-    <t>IPPF-GBR-013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-IPPF-ISL-001
-</t>
-  </si>
-  <si>
-    <t>IPPF-HND-002</t>
-  </si>
-  <si>
-    <t>IPPF-MEX-004</t>
-  </si>
-  <si>
-    <t>IPPF-CIV-008</t>
-  </si>
-  <si>
-    <t>IPPF-ARG-001</t>
-  </si>
-  <si>
-    <t>IPPF-GMB-001</t>
-  </si>
-  <si>
-    <t>IPPF-NGA-001</t>
-  </si>
-  <si>
-    <t>IPPF-GRD-001</t>
-  </si>
-  <si>
-    <t>IPPF-BDI-003</t>
-  </si>
-  <si>
-    <t>IPPF-GUY-001</t>
-  </si>
-  <si>
-    <t>IPPF-HTI-004</t>
-  </si>
-  <si>
-    <t>IPPF-HUN-004</t>
-  </si>
-  <si>
-    <t>IPPF-ARM-004</t>
-  </si>
-  <si>
-    <t>IPPF-MKW-001</t>
-  </si>
-  <si>
-    <t>IPPF-MDA-002</t>
-  </si>
-  <si>
-    <t>IPPF-URY-001</t>
-  </si>
-  <si>
-    <t>IPPF-SVN-002</t>
-  </si>
-  <si>
-    <t>IPPF-JOR-004</t>
-  </si>
-  <si>
-    <t>IPPF-BIH-002</t>
-  </si>
-  <si>
-    <t>IPPF-IDN-006</t>
-  </si>
-  <si>
-    <t>IPPF-BRA-001</t>
-  </si>
-  <si>
-    <t>IPPF-PER-003</t>
-  </si>
-  <si>
-    <t>IPPF-NGA-003</t>
-  </si>
-  <si>
-    <t>IPPF-USA-007</t>
-  </si>
-  <si>
-    <t>IPPF-IRQ-001</t>
-  </si>
-  <si>
-    <t>IPPF-IRL-002</t>
-  </si>
-  <si>
-    <t>IPPF-ISR-001</t>
-  </si>
-  <si>
-    <t>IPPF-JAM-003</t>
-  </si>
-  <si>
-    <t>IPPF-JPN-003</t>
-  </si>
-  <si>
-    <t>IPPF-JPN-002</t>
-  </si>
-  <si>
-    <t>IPPF-KAZ-001</t>
-  </si>
-  <si>
-    <t>IPPF-KIR-001</t>
-  </si>
-  <si>
-    <t>IPPF-KOR-001</t>
-  </si>
-  <si>
-    <t>IPPF-SRB-003</t>
-  </si>
-  <si>
-    <t>IPPF-UGA-006</t>
-  </si>
-  <si>
-    <t>IPPF-KGZ-001</t>
-  </si>
-  <si>
-    <t>IPPF-LVA-001</t>
-  </si>
-  <si>
-    <t>IPPF-LBN-002</t>
-  </si>
-  <si>
-    <t>IPPF-LBN-005</t>
-  </si>
-  <si>
-    <t>IPPF-LSO-001</t>
-  </si>
-  <si>
-    <t>IPPF-GHA-001</t>
-  </si>
-  <si>
-    <t>IPPF-HUN-005</t>
-  </si>
-  <si>
-    <t>IPPF-MUS-001</t>
-  </si>
-  <si>
-    <t>IPPF-TWN-002</t>
-  </si>
-  <si>
-    <t>IPPF-GUY-002</t>
-  </si>
-  <si>
-    <t>IPPF-MNG-001</t>
-  </si>
-  <si>
-    <t>IPPF-FRA-006</t>
-  </si>
-  <si>
-    <t>IPPF-GAB-001</t>
-  </si>
-  <si>
-    <t>IPPF-LUX-002</t>
-  </si>
-  <si>
-    <t>IPPF-ARG-006</t>
-  </si>
-  <si>
-    <t>IPPF-ZWE-002</t>
-  </si>
-  <si>
-    <t>IPPF-MMR-001</t>
-  </si>
-  <si>
-    <t>IPPF-NAM-002</t>
-  </si>
-  <si>
-    <t>IPPF-NZL-001</t>
-  </si>
-  <si>
-    <t>IPPF-UKR-001</t>
-  </si>
-  <si>
-    <t>IPPF-IRQ-002</t>
-  </si>
-  <si>
-    <t>IPPF-OMN-001</t>
-  </si>
-  <si>
-    <t>IPPF-PSE-001</t>
-  </si>
-  <si>
-    <t>IPPF-PNG-001</t>
-  </si>
-  <si>
-    <t>IPPF-HUN-006</t>
-  </si>
-  <si>
-    <t>IPPF-GHA-002</t>
-  </si>
-  <si>
-    <t>IPPF-LBR-002</t>
-  </si>
-  <si>
-    <t>IPPF-SLE-001</t>
-  </si>
-  <si>
-    <t>IPPF-ZAF-007</t>
-  </si>
-  <si>
-    <t>IPPF-THA-003</t>
-  </si>
-  <si>
-    <t>IPPF-ZMB-003</t>
-  </si>
-  <si>
-    <t>IPPF-USA-009</t>
-  </si>
-  <si>
-    <t>IPPF-NGA-004</t>
-  </si>
-  <si>
-    <t>IPPF-POL-005</t>
-  </si>
-  <si>
-    <t>IPPF-BGD-006</t>
-  </si>
-  <si>
-    <t>IPPF-MWI-003</t>
-  </si>
-  <si>
-    <t>IPPF-GRC-002</t>
-  </si>
-  <si>
-    <t>IPPF-DEU-003</t>
-  </si>
-  <si>
-    <t>IPPF-LAO-001</t>
-  </si>
-  <si>
-    <t>IPPF-UZB-002</t>
-  </si>
-  <si>
-    <t>IPPF-ALB-001</t>
-  </si>
-  <si>
-    <t>IPPF-BDI-002</t>
-  </si>
-  <si>
-    <t>IPPF-PAK-001</t>
-  </si>
-  <si>
-    <t>IPPF-FJI-003</t>
-  </si>
-  <si>
-    <t>IPPF-ZAF-004</t>
-  </si>
-  <si>
-    <t>IPPF-KGZ-002</t>
-  </si>
-  <si>
-    <t>IPPF-KHM-001</t>
-  </si>
-  <si>
-    <t>IPPF-SSD-001</t>
-  </si>
-  <si>
-    <t>IPPF-KEN-016</t>
-  </si>
-  <si>
-    <t>IPPF-UGA-008</t>
-  </si>
-  <si>
-    <t>IPPF-BTN-001</t>
-  </si>
-  <si>
-    <t>IPPF-MWI-004</t>
-  </si>
-  <si>
-    <t>IPPF-SWE-001</t>
-  </si>
-  <si>
-    <t>IPPF-RUS-001</t>
-  </si>
-  <si>
-    <t>IPPF-NLD-003</t>
-  </si>
-  <si>
-    <t>IPPF-MYS-004</t>
-  </si>
-  <si>
-    <t>IPPF-LCA-001</t>
-  </si>
-  <si>
-    <t>IPPF-WSM-001</t>
-  </si>
-  <si>
-    <t>IPPF-CHE-003</t>
-  </si>
-  <si>
-    <t>IPPF-MYS-005</t>
-  </si>
-  <si>
-    <t>IPPF-LTU-001</t>
-  </si>
-  <si>
-    <t>IPPF-BEL-001</t>
-  </si>
-  <si>
-    <t>IPPF-DNK-001</t>
-  </si>
-  <si>
-    <t>IPPF-NOR-001</t>
-  </si>
-  <si>
-    <t>IPPF-ZAF-005</t>
-  </si>
-  <si>
-    <t>IPPF-SGN-001</t>
-  </si>
-  <si>
-    <t>IPPF-SVK-004</t>
-  </si>
-  <si>
-    <t>IPPF-CUB-002</t>
-  </si>
-  <si>
-    <t>IPPF-ROU-001</t>
-  </si>
-  <si>
-    <t>IPPF-MDA-005</t>
-  </si>
-  <si>
-    <t>IPPF-MDV-001</t>
-  </si>
-  <si>
-    <t>IPPF-SOM-001</t>
-  </si>
-  <si>
-    <t>IPPF-COD-007</t>
-  </si>
-  <si>
-    <t>IPPF-ZAF-006</t>
-  </si>
-  <si>
-    <t>IPPF-CZE-002</t>
-  </si>
-  <si>
-    <t>IPPF-UGA-010</t>
-  </si>
-  <si>
-    <t>IPPF-VCT-001</t>
-  </si>
-  <si>
-    <t>IPPF-SUR-001</t>
-  </si>
-  <si>
-    <t>IPPF-SDN-001</t>
-  </si>
-  <si>
-    <t>IPPF-SYR-001</t>
-  </si>
-  <si>
-    <t>IPPF-TUR-006</t>
-  </si>
-  <si>
-    <t>IPPF-TJK-002</t>
-  </si>
-  <si>
-    <t>IPPF-ETH-016</t>
-  </si>
-  <si>
-    <t>IPPF-BRB-001</t>
-  </si>
-  <si>
-    <t>IPPF-UGA-011</t>
-  </si>
-  <si>
-    <t>IPPF-GBR-004</t>
-  </si>
-  <si>
-    <t>IPPF-IDN-005</t>
-  </si>
-  <si>
-    <t>IPPF-ZAF-008</t>
-  </si>
-  <si>
-    <t>IPPF-TON-001</t>
-  </si>
-  <si>
-    <t>IPPF-POL-008</t>
-  </si>
-  <si>
-    <t>IPPF-TKM-001</t>
-  </si>
-  <si>
-    <t>IPPF-UGA-012</t>
-  </si>
-  <si>
-    <t>IPPF-TUV-001</t>
-  </si>
-  <si>
-    <t>IPPF-ITA-004</t>
-  </si>
-  <si>
-    <t>IPPF-BEL-008</t>
-  </si>
-  <si>
-    <t>IPPF-TZA-002</t>
-  </si>
-  <si>
-    <t>IPPF-UZB-001</t>
-  </si>
-  <si>
-    <t>IPPF-FIN-001</t>
-  </si>
-  <si>
-    <t>IPPF-VUT-001</t>
-  </si>
-  <si>
-    <t>IPPF-VNM-001</t>
-  </si>
-  <si>
-    <t>IPPF-NGA-005</t>
-  </si>
-  <si>
-    <t>IPPF-ESP-002</t>
-  </si>
-  <si>
-    <t>IPPF-YEM-002</t>
-  </si>
-  <si>
-    <t>IPPF-YEM-001</t>
-  </si>
-  <si>
-    <t>IPPF-MHL-001</t>
-  </si>
-  <si>
-    <t>IPPF-ZWE-004</t>
+    <t>ZBkM8lmhvSR</t>
   </si>
 </sst>
 </file>
@@ -2091,7 +775,8 @@
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.6328125" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="13.453125" style="3" customWidth="1"/>
+    <col min="2" max="2" width="13.453125" style="3" customWidth="1"/>
+    <col min="3" max="3" width="12.90625" style="3" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="15" style="3" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="10.08984375" style="3" bestFit="1" customWidth="1"/>
     <col min="6" max="16384" width="8.7265625" style="3"/>
@@ -2108,3220 +793,2188 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A2" s="5" t="s">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="C2" s="1">
+        <v>7010600031</v>
+      </c>
+      <c r="D2" s="4"/>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="C3" s="1">
+        <v>5080200151</v>
+      </c>
+      <c r="D3" s="4"/>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="C4" s="1">
+        <v>7050200101</v>
+      </c>
+      <c r="D4" s="4"/>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="C5" s="1">
+        <v>7070600031</v>
+      </c>
+      <c r="D5" s="4"/>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="C6" s="1">
+        <v>5100300131</v>
+      </c>
+      <c r="D6" s="4"/>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="C7" s="1">
+        <v>5040900251</v>
+      </c>
+      <c r="D7" s="4"/>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="C8" s="1">
+        <v>3110500061</v>
+      </c>
+      <c r="D8" s="4"/>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="C9" s="1">
+        <v>3050400331</v>
+      </c>
+      <c r="D9" s="4"/>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="C10" s="1">
+        <v>7070500061</v>
+      </c>
+      <c r="D10" s="4"/>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="C11" s="1">
+        <v>6060800041</v>
+      </c>
+      <c r="D11" s="4"/>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="C12" s="1">
+        <v>1110700011</v>
+      </c>
+      <c r="D12" s="4"/>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="C13" s="1">
+        <v>3100400021</v>
+      </c>
+      <c r="D13" s="4"/>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="C14" s="1">
+        <v>3060800151</v>
+      </c>
+      <c r="D14" s="4"/>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="C15" s="1">
+        <v>3120600161</v>
+      </c>
+      <c r="D15" s="4"/>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="C16" s="1">
+        <v>2041500061</v>
+      </c>
+      <c r="D16" s="4"/>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="C17" s="1">
+        <v>1111400121</v>
+      </c>
+      <c r="D17" s="4"/>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="C18" s="1">
+        <v>5060100041</v>
+      </c>
+      <c r="D18" s="4"/>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="C19" s="1">
+        <v>7010300151</v>
+      </c>
+      <c r="D19" s="4"/>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="C20" s="1">
+        <v>2011300121</v>
+      </c>
+      <c r="D20" s="4"/>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="C21" s="1">
+        <v>7090500031</v>
+      </c>
+      <c r="D21" s="4"/>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="C22" s="1">
+        <v>2031500382</v>
+      </c>
+      <c r="D22" s="4"/>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="C23" s="1">
+        <v>4060500081</v>
+      </c>
+      <c r="D23" s="4"/>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="C24" s="1">
+        <v>11111111111</v>
+      </c>
+      <c r="D24" s="4"/>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="C25" s="1">
+        <v>5090700051</v>
+      </c>
+      <c r="D25" s="4"/>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="C26" s="1">
+        <v>2021700051</v>
+      </c>
+      <c r="D26" s="4"/>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="C27" s="1">
+        <v>5070300021</v>
+      </c>
+      <c r="D27" s="4"/>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="C28" s="1">
+        <v>3090500142</v>
+      </c>
+      <c r="D28" s="4"/>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="C29" s="1">
+        <v>5120700081</v>
+      </c>
+      <c r="D29" s="4"/>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="C30" s="1">
+        <v>7081000021</v>
+      </c>
+      <c r="D30" s="4"/>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="C31" s="1">
+        <v>3070200031</v>
+      </c>
+      <c r="D31" s="4"/>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="C32" s="1">
+        <v>4090900191</v>
+      </c>
+      <c r="D32" s="4"/>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B33" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="C33" s="1">
+        <v>6060700031</v>
+      </c>
+      <c r="D33" s="4"/>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="C34" s="1">
+        <v>4070200081</v>
+      </c>
+      <c r="D34" s="4"/>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="C35" s="1">
+        <v>40807000811</v>
+      </c>
+      <c r="D35" s="4"/>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A36" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="C36" s="1">
+        <v>3060800491</v>
+      </c>
+      <c r="D36" s="4"/>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A37" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B37" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="C37" s="1">
+        <v>7030300031</v>
+      </c>
+      <c r="D37" s="4"/>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A38" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="B38" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="C38" s="1">
+        <v>1130900041</v>
+      </c>
+      <c r="D38" s="4"/>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A39" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B39" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="C39" s="1">
+        <v>1070400051</v>
+      </c>
+      <c r="D39" s="4"/>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A40" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B40" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="C40" s="1">
+        <v>7040800071</v>
+      </c>
+      <c r="D40" s="4"/>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A41" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B41" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="C41" s="1">
+        <v>3010900261</v>
+      </c>
+      <c r="D41" s="4"/>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A42" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B42" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="C42" s="1">
+        <v>5100200421</v>
+      </c>
+      <c r="D42" s="4"/>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A43" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B43" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="C43" s="1">
+        <v>3060800471</v>
+      </c>
+      <c r="D43" s="4"/>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A44" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B44" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="C44" s="1">
+        <v>4040600051</v>
+      </c>
+      <c r="D44" s="4"/>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A45" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B45" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="C45" s="1">
+        <v>1121400751</v>
+      </c>
+      <c r="D45" s="4"/>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A46" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B46" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="C46" s="1">
+        <v>1100300051</v>
+      </c>
+      <c r="D46" s="4"/>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A47" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B47" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="C47" s="1">
+        <v>7060500061</v>
+      </c>
+      <c r="D47" s="4"/>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A48" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B48" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="C48" s="1">
+        <v>3080200472</v>
+      </c>
+      <c r="D48" s="4"/>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A49" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B49" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="C49" s="1">
+        <v>5030400031</v>
+      </c>
+      <c r="D49" s="4"/>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A50" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B50" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="C50" s="1">
+        <v>6090700031</v>
+      </c>
+      <c r="D50" s="4"/>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A51" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B51" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="C51" s="1">
+        <v>6100400021</v>
+      </c>
+      <c r="D51" s="4"/>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A52" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B52" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="C52" s="1">
+        <v>4090100061</v>
+      </c>
+      <c r="D52" s="4"/>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A53" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B53" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="C53" s="1">
+        <v>2070800051</v>
+      </c>
+      <c r="D53" s="4"/>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A54" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B54" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="C54" s="1">
+        <v>2080900031</v>
+      </c>
+      <c r="D54" s="4"/>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A55" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B55" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="C55" s="1">
+        <v>3060800461</v>
+      </c>
+      <c r="D55" s="4"/>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A56" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B56" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="C56" s="1">
+        <v>3040600221</v>
+      </c>
+      <c r="D56" s="4"/>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A57" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B57" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="C57" s="1">
+        <v>6080400051</v>
+      </c>
+      <c r="D57" s="4"/>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A58" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B58" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="C58" s="1">
+        <v>7040500041</v>
+      </c>
+      <c r="D58" s="4"/>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A59" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B59" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="C59" s="1">
+        <v>3020700101</v>
+      </c>
+      <c r="D59" s="4"/>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A60" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B60" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="C60" s="1">
+        <v>4080700081</v>
+      </c>
+      <c r="D60" s="4"/>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A61" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B61" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="C61" s="1">
+        <v>5110600241</v>
+      </c>
+      <c r="D61" s="4"/>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A62" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B62" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="C62" s="1">
+        <v>7090400101</v>
+      </c>
+      <c r="D62" s="4"/>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A63" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B63" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="C63" s="1">
+        <v>3080200011</v>
+      </c>
+      <c r="D63" s="4"/>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A64" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B64" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="C64" s="1">
+        <v>7070400012</v>
+      </c>
+      <c r="D64" s="4"/>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A65" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B65" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="C65" s="1">
+        <v>4050400361</v>
+      </c>
+      <c r="D65" s="4"/>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A66" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B66" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="C66" s="1">
+        <v>7050500021</v>
+      </c>
+      <c r="D66" s="4"/>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A67" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B67" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="C67" s="1">
+        <v>5081100031</v>
+      </c>
+      <c r="D67" s="4"/>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A68" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B68" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="C68" s="1">
+        <v>5020700031</v>
+      </c>
+      <c r="D68" s="4"/>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A69" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B69" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="C69" s="1">
+        <v>2052000031</v>
+      </c>
+      <c r="D69" s="4"/>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A70" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B70" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="C70" s="1">
+        <v>3060800481</v>
+      </c>
+      <c r="D70" s="4"/>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A71" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B71" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="C71" s="1">
+        <v>7020600041</v>
+      </c>
+      <c r="D71" s="4"/>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A72" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B72" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="C72" s="1">
+        <v>6060500031</v>
+      </c>
+      <c r="D72" s="4"/>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A73" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B73" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="C73" s="1">
+        <v>7081300151</v>
+      </c>
+      <c r="D73" s="4"/>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A74" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="B74" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="C74" s="1">
+        <v>2031500181</v>
+      </c>
+      <c r="D74" s="4"/>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A75" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B75" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="C75" s="1">
+        <v>3130400221</v>
+      </c>
+      <c r="D75" s="4"/>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A76" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B76" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="C76" s="1">
+        <v>1040200041</v>
+      </c>
+      <c r="D76" s="4"/>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A77" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B77" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="C77" s="1">
+        <v>7070800091</v>
+      </c>
+      <c r="D77" s="4"/>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A78" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B78" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="C78" s="1">
+        <v>5060500162</v>
+      </c>
+      <c r="D78" s="4"/>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A79" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B79" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="C79" s="1">
+        <v>3130700031</v>
+      </c>
+      <c r="D79" s="4"/>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A80" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B80" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="C80" s="1">
+        <v>6100600121</v>
+      </c>
+      <c r="D80" s="4"/>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A81" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B81" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="C81" s="1">
+        <v>1140300031</v>
+      </c>
+      <c r="D81" s="4"/>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A82" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="B82" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="C82" s="1">
+        <v>5010200101</v>
+      </c>
+      <c r="D82" s="4"/>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A83" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B83" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="C83" s="1">
+        <v>4110100221</v>
+      </c>
+      <c r="D83" s="4"/>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A84" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B84" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="C84" s="1">
+        <v>7080700011</v>
+      </c>
+      <c r="D84" s="4"/>
+    </row>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A85" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B85" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="C85" s="1">
+        <v>1130100011</v>
+      </c>
+      <c r="D85" s="4"/>
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A86" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B86" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="C86" s="1">
+        <v>2061700051</v>
+      </c>
+      <c r="D86" s="4"/>
+    </row>
+    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A87" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B87" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="C87" s="1">
+        <v>5090600091</v>
+      </c>
+      <c r="D87" s="4"/>
+    </row>
+    <row r="88" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="A88" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="B88" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="C88" s="5">
+        <v>7080300071</v>
+      </c>
+      <c r="D88" s="4"/>
+    </row>
+    <row r="89" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="A89" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B89" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="C89" s="5">
+        <v>1020600071</v>
+      </c>
+      <c r="D89" s="4"/>
+    </row>
+    <row r="90" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="A90" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="B90" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="C90" s="5">
+        <v>4100300051</v>
+      </c>
+      <c r="D90" s="4"/>
+    </row>
+    <row r="91" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="A91" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="B91" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="C91" s="5">
+        <v>5050400281</v>
+      </c>
+      <c r="D91" s="4"/>
+    </row>
+    <row r="92" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="A92" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B92" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="C92" s="5">
+        <v>2020100061</v>
+      </c>
+      <c r="D92" s="4"/>
+    </row>
+    <row r="93" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="A93" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="B93" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="C93" s="5">
+        <v>6050600031</v>
+      </c>
+      <c r="D93" s="4"/>
+    </row>
+    <row r="94" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="A94" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B94" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="C94" s="5">
+        <v>2080700241</v>
+      </c>
+      <c r="D94" s="4"/>
+    </row>
+    <row r="95" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="A95" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="B95" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="C95" s="5">
+        <v>6100800071</v>
+      </c>
+      <c r="D95" s="4"/>
+    </row>
+    <row r="96" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="A96" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>272</v>
-      </c>
-      <c r="D2" s="4"/>
-    </row>
-    <row r="3" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>273</v>
-      </c>
-      <c r="D3" s="4"/>
-    </row>
-    <row r="4" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>274</v>
-      </c>
-      <c r="D4" s="4"/>
-    </row>
-    <row r="5" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>275</v>
-      </c>
-      <c r="D5" s="4"/>
-    </row>
-    <row r="6" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>276</v>
-      </c>
-      <c r="D6" s="4"/>
-    </row>
-    <row r="7" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A7" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>277</v>
-      </c>
-      <c r="D7" s="4"/>
-    </row>
-    <row r="8" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A8" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>278</v>
-      </c>
-      <c r="D8" s="4"/>
-    </row>
-    <row r="9" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A9" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>279</v>
-      </c>
-      <c r="D9" s="4"/>
-    </row>
-    <row r="10" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A10" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>280</v>
-      </c>
-      <c r="D10" s="4"/>
-    </row>
-    <row r="11" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A11" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>281</v>
-      </c>
-      <c r="D11" s="4"/>
-    </row>
-    <row r="12" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A12" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="B12" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>282</v>
-      </c>
-      <c r="D12" s="4"/>
-    </row>
-    <row r="13" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A13" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B13" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>283</v>
-      </c>
-      <c r="D13" s="4"/>
-    </row>
-    <row r="14" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A14" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="B14" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>284</v>
-      </c>
-      <c r="D14" s="4"/>
-    </row>
-    <row r="15" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A15" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="B15" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>285</v>
-      </c>
-      <c r="D15" s="4"/>
-    </row>
-    <row r="16" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A16" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="B16" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C16" s="5" t="s">
-        <v>286</v>
-      </c>
-      <c r="D16" s="4"/>
-    </row>
-    <row r="17" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A17" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="B17" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>287</v>
-      </c>
-      <c r="D17" s="4"/>
-    </row>
-    <row r="18" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A18" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="B18" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C18" s="5" t="s">
-        <v>288</v>
-      </c>
-      <c r="D18" s="4"/>
-    </row>
-    <row r="19" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A19" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="B19" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C19" s="5" t="s">
-        <v>289</v>
-      </c>
-      <c r="D19" s="4"/>
-    </row>
-    <row r="20" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A20" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="B20" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C20" s="5" t="s">
-        <v>290</v>
-      </c>
-      <c r="D20" s="4"/>
-    </row>
-    <row r="21" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A21" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="B21" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C21" s="5" t="s">
-        <v>291</v>
-      </c>
-      <c r="D21" s="4"/>
-    </row>
-    <row r="22" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A22" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="B22" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C22" s="5" t="s">
-        <v>292</v>
-      </c>
-      <c r="D22" s="4"/>
-    </row>
-    <row r="23" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A23" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="B23" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C23" s="5" t="s">
-        <v>293</v>
-      </c>
-      <c r="D23" s="4"/>
-    </row>
-    <row r="24" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A24" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="B24" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C24" s="5" t="s">
-        <v>294</v>
-      </c>
-      <c r="D24" s="4"/>
-    </row>
-    <row r="25" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A25" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="B25" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C25" s="5" t="s">
-        <v>295</v>
-      </c>
-      <c r="D25" s="4"/>
-    </row>
-    <row r="26" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A26" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="B26" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C26" s="5" t="s">
-        <v>296</v>
-      </c>
-      <c r="D26" s="4"/>
-    </row>
-    <row r="27" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A27" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="B27" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C27" s="5" t="s">
-        <v>297</v>
-      </c>
-      <c r="D27" s="4"/>
-    </row>
-    <row r="28" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A28" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="B28" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C28" s="5" t="s">
-        <v>298</v>
-      </c>
-      <c r="D28" s="4"/>
-    </row>
-    <row r="29" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A29" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="B29" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C29" s="5" t="s">
-        <v>299</v>
-      </c>
-      <c r="D29" s="4"/>
-    </row>
-    <row r="30" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A30" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="B30" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C30" s="5" t="s">
-        <v>300</v>
-      </c>
-      <c r="D30" s="4"/>
-    </row>
-    <row r="31" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A31" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="B31" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C31" s="5" t="s">
-        <v>301</v>
-      </c>
-      <c r="D31" s="4"/>
-    </row>
-    <row r="32" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A32" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="B32" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C32" s="5" t="s">
-        <v>302</v>
-      </c>
-      <c r="D32" s="4"/>
-    </row>
-    <row r="33" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A33" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="B33" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C33" s="5" t="s">
-        <v>303</v>
-      </c>
-      <c r="D33" s="4"/>
-    </row>
-    <row r="34" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A34" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="B34" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C34" s="5" t="s">
-        <v>304</v>
-      </c>
-      <c r="D34" s="4"/>
-    </row>
-    <row r="35" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A35" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="B35" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C35" s="5" t="s">
-        <v>305</v>
-      </c>
-      <c r="D35" s="4"/>
-    </row>
-    <row r="36" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A36" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B36" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C36" s="5" t="s">
-        <v>306</v>
-      </c>
-      <c r="D36" s="4"/>
-    </row>
-    <row r="37" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A37" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B37" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C37" s="5" t="s">
-        <v>307</v>
-      </c>
-      <c r="D37" s="4"/>
-    </row>
-    <row r="38" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A38" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B38" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C38" s="5" t="s">
-        <v>308</v>
-      </c>
-      <c r="D38" s="4"/>
-    </row>
-    <row r="39" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A39" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B39" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C39" s="5" t="s">
-        <v>309</v>
-      </c>
-      <c r="D39" s="4"/>
-    </row>
-    <row r="40" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A40" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B40" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C40" s="5" t="s">
-        <v>310</v>
-      </c>
-      <c r="D40" s="4"/>
-    </row>
-    <row r="41" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A41" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B41" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C41" s="5" t="s">
-        <v>311</v>
-      </c>
-      <c r="D41" s="4"/>
-    </row>
-    <row r="42" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A42" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B42" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C42" s="5" t="s">
-        <v>312</v>
-      </c>
-      <c r="D42" s="4"/>
-    </row>
-    <row r="43" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A43" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B43" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C43" s="5" t="s">
-        <v>313</v>
-      </c>
-      <c r="D43" s="4"/>
-    </row>
-    <row r="44" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A44" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B44" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C44" s="5" t="s">
-        <v>314</v>
-      </c>
-      <c r="D44" s="4"/>
-    </row>
-    <row r="45" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A45" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="B45" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C45" s="5" t="s">
-        <v>315</v>
-      </c>
-      <c r="D45" s="4"/>
-    </row>
-    <row r="46" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A46" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="B46" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C46" s="5" t="s">
-        <v>316</v>
-      </c>
-      <c r="D46" s="4"/>
-    </row>
-    <row r="47" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A47" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="B47" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C47" s="5" t="s">
-        <v>317</v>
-      </c>
-      <c r="D47" s="4"/>
-    </row>
-    <row r="48" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A48" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="B48" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C48" s="5" t="s">
-        <v>318</v>
-      </c>
-      <c r="D48" s="4"/>
-    </row>
-    <row r="49" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A49" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="B49" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C49" s="5" t="s">
-        <v>319</v>
-      </c>
-      <c r="D49" s="4"/>
-    </row>
-    <row r="50" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A50" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="B50" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C50" s="5" t="s">
-        <v>320</v>
-      </c>
-      <c r="D50" s="4"/>
-    </row>
-    <row r="51" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A51" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="B51" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C51" s="5" t="s">
-        <v>321</v>
-      </c>
-      <c r="D51" s="4"/>
-    </row>
-    <row r="52" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A52" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="B52" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C52" s="5" t="s">
-        <v>322</v>
-      </c>
-      <c r="D52" s="4"/>
-    </row>
-    <row r="53" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A53" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="B53" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C53" s="5" t="s">
-        <v>323</v>
-      </c>
-      <c r="D53" s="4"/>
-    </row>
-    <row r="54" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A54" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="B54" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C54" s="5" t="s">
-        <v>324</v>
-      </c>
-      <c r="D54" s="4"/>
-    </row>
-    <row r="55" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A55" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="B55" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C55" s="5" t="s">
-        <v>325</v>
-      </c>
-      <c r="D55" s="4"/>
-    </row>
-    <row r="56" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A56" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="B56" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C56" s="5" t="s">
-        <v>326</v>
-      </c>
-      <c r="D56" s="4"/>
-    </row>
-    <row r="57" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A57" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="B57" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C57" s="5" t="s">
-        <v>327</v>
-      </c>
-      <c r="D57" s="4"/>
-    </row>
-    <row r="58" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A58" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="B58" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C58" s="5" t="s">
-        <v>328</v>
-      </c>
-      <c r="D58" s="4"/>
-    </row>
-    <row r="59" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A59" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="B59" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C59" s="5" t="s">
-        <v>329</v>
-      </c>
-      <c r="D59" s="4"/>
-    </row>
-    <row r="60" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A60" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="B60" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C60" s="5" t="s">
-        <v>330</v>
-      </c>
-      <c r="D60" s="4"/>
-    </row>
-    <row r="61" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A61" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="B61" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C61" s="5" t="s">
-        <v>331</v>
-      </c>
-      <c r="D61" s="4"/>
-    </row>
-    <row r="62" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A62" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="B62" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C62" s="5" t="s">
-        <v>332</v>
-      </c>
-      <c r="D62" s="4"/>
-    </row>
-    <row r="63" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A63" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="B63" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C63" s="5" t="s">
-        <v>333</v>
-      </c>
-      <c r="D63" s="4"/>
-    </row>
-    <row r="64" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A64" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="B64" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C64" s="5" t="s">
-        <v>334</v>
-      </c>
-      <c r="D64" s="4"/>
-    </row>
-    <row r="65" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A65" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="B65" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C65" s="5" t="s">
-        <v>335</v>
-      </c>
-      <c r="D65" s="4"/>
-    </row>
-    <row r="66" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A66" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="B66" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C66" s="5" t="s">
-        <v>336</v>
-      </c>
-      <c r="D66" s="4"/>
-    </row>
-    <row r="67" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A67" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="B67" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C67" s="5" t="s">
-        <v>337</v>
-      </c>
-      <c r="D67" s="4"/>
-    </row>
-    <row r="68" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A68" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="B68" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C68" s="5" t="s">
-        <v>338</v>
-      </c>
-      <c r="D68" s="4"/>
-    </row>
-    <row r="69" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A69" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="B69" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C69" s="5" t="s">
-        <v>339</v>
-      </c>
-      <c r="D69" s="4"/>
-    </row>
-    <row r="70" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A70" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="B70" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C70" s="5" t="s">
-        <v>340</v>
-      </c>
-      <c r="D70" s="4"/>
-    </row>
-    <row r="71" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A71" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="B71" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C71" s="5" t="s">
-        <v>341</v>
-      </c>
-      <c r="D71" s="4"/>
-    </row>
-    <row r="72" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A72" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="B72" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C72" s="5" t="s">
-        <v>342</v>
-      </c>
-      <c r="D72" s="4"/>
-    </row>
-    <row r="73" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A73" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="B73" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C73" s="5" t="s">
-        <v>343</v>
-      </c>
-      <c r="D73" s="4"/>
-    </row>
-    <row r="74" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A74" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="B74" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C74" s="5" t="s">
-        <v>344</v>
-      </c>
-      <c r="D74" s="4"/>
-    </row>
-    <row r="75" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A75" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="B75" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C75" s="5" t="s">
-        <v>345</v>
-      </c>
-      <c r="D75" s="4"/>
-    </row>
-    <row r="76" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A76" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="B76" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C76" s="5" t="s">
-        <v>346</v>
-      </c>
-      <c r="D76" s="4"/>
-    </row>
-    <row r="77" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A77" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="B77" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C77" s="5" t="s">
-        <v>347</v>
-      </c>
-      <c r="D77" s="4"/>
-    </row>
-    <row r="78" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A78" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="B78" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C78" s="5" t="s">
-        <v>348</v>
-      </c>
-      <c r="D78" s="4"/>
-    </row>
-    <row r="79" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A79" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="B79" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C79" s="5" t="s">
-        <v>348</v>
-      </c>
-      <c r="D79" s="4"/>
-    </row>
-    <row r="80" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A80" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="B80" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C80" s="5" t="s">
-        <v>349</v>
-      </c>
-      <c r="D80" s="4"/>
-    </row>
-    <row r="81" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A81" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="B81" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C81" s="5" t="s">
-        <v>350</v>
-      </c>
-      <c r="D81" s="4"/>
-    </row>
-    <row r="82" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A82" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="B82" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C82" s="5" t="s">
-        <v>351</v>
-      </c>
-      <c r="D82" s="4"/>
-    </row>
-    <row r="83" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A83" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="B83" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C83" s="5" t="s">
-        <v>352</v>
-      </c>
-      <c r="D83" s="4"/>
-    </row>
-    <row r="84" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A84" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="B84" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C84" s="5" t="s">
-        <v>353</v>
-      </c>
-      <c r="D84" s="4"/>
-    </row>
-    <row r="85" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A85" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="B85" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C85" s="5" t="s">
-        <v>354</v>
-      </c>
-      <c r="D85" s="4"/>
-    </row>
-    <row r="86" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A86" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="B86" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C86" s="5" t="s">
-        <v>355</v>
-      </c>
-      <c r="D86" s="4"/>
-    </row>
-    <row r="87" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A87" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="B87" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C87" s="5" t="s">
-        <v>356</v>
-      </c>
-      <c r="D87" s="4"/>
-    </row>
-    <row r="88" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A88" s="5" t="s">
+      <c r="B96" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="B88" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C88" s="5" t="s">
-        <v>357</v>
-      </c>
-      <c r="D88" s="4"/>
-    </row>
-    <row r="89" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A89" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="B89" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C89" s="5" t="s">
-        <v>358</v>
-      </c>
-      <c r="D89" s="4"/>
-    </row>
-    <row r="90" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A90" s="5" t="s">
-        <v>91</v>
-      </c>
-      <c r="B90" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C90" s="5" t="s">
-        <v>359</v>
-      </c>
-      <c r="D90" s="4"/>
-    </row>
-    <row r="91" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A91" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="B91" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C91" s="5" t="s">
-        <v>360</v>
-      </c>
-      <c r="D91" s="4"/>
-    </row>
-    <row r="92" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A92" s="5" t="s">
-        <v>93</v>
-      </c>
-      <c r="B92" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C92" s="5" t="s">
-        <v>361</v>
-      </c>
-      <c r="D92" s="4"/>
-    </row>
-    <row r="93" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A93" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="B93" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C93" s="5" t="s">
-        <v>362</v>
-      </c>
-      <c r="D93" s="4"/>
-    </row>
-    <row r="94" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A94" s="5" t="s">
-        <v>95</v>
-      </c>
-      <c r="B94" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C94" s="5" t="s">
-        <v>363</v>
-      </c>
-      <c r="D94" s="4"/>
-    </row>
-    <row r="95" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A95" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="B95" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C95" s="5" t="s">
-        <v>364</v>
-      </c>
-      <c r="D95" s="4"/>
-    </row>
-    <row r="96" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A96" s="5" t="s">
-        <v>97</v>
-      </c>
-      <c r="B96" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C96" s="5" t="s">
-        <v>365</v>
+      <c r="C96" s="5">
+        <v>1090400051</v>
       </c>
       <c r="D96" s="4"/>
     </row>
     <row r="97" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
       <c r="A97" s="5" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B97" s="6" t="s">
-        <v>271</v>
+        <v>89</v>
       </c>
-      <c r="C97" s="5" t="s">
-        <v>366</v>
+      <c r="C97" s="5">
+        <v>4010900071</v>
       </c>
       <c r="D97" s="4"/>
     </row>
     <row r="98" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A98" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="B98" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C98" s="5" t="s">
-        <v>367</v>
-      </c>
+      <c r="A98" s="5"/>
+      <c r="B98" s="6"/>
+      <c r="C98" s="5"/>
       <c r="D98" s="4"/>
     </row>
     <row r="99" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A99" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="B99" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C99" s="5" t="s">
-        <v>368</v>
-      </c>
+      <c r="A99" s="5"/>
+      <c r="B99" s="6"/>
+      <c r="C99" s="5"/>
       <c r="D99" s="4"/>
     </row>
     <row r="100" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A100" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="B100" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C100" s="5" t="s">
-        <v>369</v>
-      </c>
+      <c r="A100" s="5"/>
+      <c r="B100" s="6"/>
+      <c r="C100" s="5"/>
       <c r="D100" s="4"/>
     </row>
     <row r="101" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A101" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="B101" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C101" s="5" t="s">
-        <v>370</v>
-      </c>
+      <c r="A101" s="5"/>
+      <c r="B101" s="6"/>
+      <c r="C101" s="5"/>
       <c r="D101" s="4"/>
     </row>
     <row r="102" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A102" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="B102" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C102" s="5" t="s">
-        <v>371</v>
-      </c>
+      <c r="A102" s="5"/>
+      <c r="B102" s="6"/>
+      <c r="C102" s="5"/>
       <c r="D102" s="4"/>
     </row>
     <row r="103" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A103" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="B103" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C103" s="5" t="s">
-        <v>372</v>
-      </c>
+      <c r="A103" s="5"/>
+      <c r="B103" s="6"/>
+      <c r="C103" s="5"/>
       <c r="D103" s="4"/>
     </row>
     <row r="104" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A104" s="5" t="s">
-        <v>105</v>
-      </c>
-      <c r="B104" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C104" s="5" t="s">
-        <v>373</v>
-      </c>
+      <c r="A104" s="5"/>
+      <c r="B104" s="6"/>
+      <c r="C104" s="5"/>
       <c r="D104" s="4"/>
     </row>
     <row r="105" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A105" s="5" t="s">
-        <v>106</v>
-      </c>
-      <c r="B105" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C105" s="5" t="s">
-        <v>374</v>
-      </c>
+      <c r="A105" s="5"/>
+      <c r="B105" s="6"/>
+      <c r="C105" s="5"/>
       <c r="D105" s="4"/>
     </row>
     <row r="106" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A106" s="5" t="s">
-        <v>107</v>
-      </c>
-      <c r="B106" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C106" s="5" t="s">
-        <v>375</v>
-      </c>
+      <c r="A106" s="5"/>
+      <c r="B106" s="6"/>
+      <c r="C106" s="5"/>
       <c r="D106" s="4"/>
     </row>
     <row r="107" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A107" s="5" t="s">
-        <v>108</v>
-      </c>
-      <c r="B107" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C107" s="5" t="s">
-        <v>376</v>
-      </c>
+      <c r="A107" s="5"/>
+      <c r="B107" s="6"/>
+      <c r="C107" s="5"/>
       <c r="D107" s="4"/>
     </row>
     <row r="108" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A108" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="B108" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C108" s="5" t="s">
-        <v>377</v>
-      </c>
+      <c r="A108" s="5"/>
+      <c r="B108" s="6"/>
+      <c r="C108" s="5"/>
       <c r="D108" s="4"/>
     </row>
     <row r="109" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A109" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="B109" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C109" s="5" t="s">
-        <v>378</v>
-      </c>
+      <c r="A109" s="5"/>
+      <c r="B109" s="6"/>
+      <c r="C109" s="5"/>
       <c r="D109" s="4"/>
     </row>
     <row r="110" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A110" s="5" t="s">
-        <v>111</v>
-      </c>
-      <c r="B110" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C110" s="5" t="s">
-        <v>379</v>
-      </c>
+      <c r="A110" s="5"/>
+      <c r="B110" s="6"/>
+      <c r="C110" s="5"/>
       <c r="D110" s="4"/>
     </row>
     <row r="111" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A111" s="5" t="s">
-        <v>112</v>
-      </c>
-      <c r="B111" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C111" s="5" t="s">
-        <v>380</v>
-      </c>
+      <c r="A111" s="5"/>
+      <c r="B111" s="6"/>
+      <c r="C111" s="5"/>
       <c r="D111" s="4"/>
     </row>
     <row r="112" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A112" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="B112" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C112" s="5" t="s">
-        <v>381</v>
-      </c>
+      <c r="A112" s="5"/>
+      <c r="B112" s="6"/>
+      <c r="C112" s="5"/>
       <c r="D112" s="4"/>
     </row>
     <row r="113" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A113" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="B113" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C113" s="5" t="s">
-        <v>382</v>
-      </c>
+      <c r="A113" s="5"/>
+      <c r="B113" s="6"/>
+      <c r="C113" s="5"/>
       <c r="D113" s="4"/>
     </row>
     <row r="114" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A114" s="5" t="s">
-        <v>115</v>
-      </c>
-      <c r="B114" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C114" s="5" t="s">
-        <v>383</v>
-      </c>
+      <c r="A114" s="5"/>
+      <c r="B114" s="6"/>
+      <c r="C114" s="5"/>
       <c r="D114" s="4"/>
     </row>
     <row r="115" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A115" s="5" t="s">
-        <v>116</v>
-      </c>
-      <c r="B115" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C115" s="5" t="s">
-        <v>384</v>
-      </c>
+      <c r="A115" s="5"/>
+      <c r="B115" s="6"/>
+      <c r="C115" s="5"/>
       <c r="D115" s="4"/>
     </row>
     <row r="116" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A116" s="5" t="s">
-        <v>117</v>
-      </c>
-      <c r="B116" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C116" s="5" t="s">
-        <v>385</v>
-      </c>
+      <c r="A116" s="5"/>
+      <c r="B116" s="6"/>
+      <c r="C116" s="5"/>
       <c r="D116" s="4"/>
     </row>
     <row r="117" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A117" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="B117" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C117" s="5" t="s">
-        <v>386</v>
-      </c>
+      <c r="A117" s="5"/>
+      <c r="B117" s="6"/>
+      <c r="C117" s="5"/>
       <c r="D117" s="4"/>
     </row>
     <row r="118" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A118" s="5" t="s">
-        <v>119</v>
-      </c>
-      <c r="B118" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C118" s="5" t="s">
-        <v>387</v>
-      </c>
+      <c r="A118" s="5"/>
+      <c r="B118" s="6"/>
+      <c r="C118" s="5"/>
       <c r="D118" s="4"/>
     </row>
     <row r="119" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A119" s="5" t="s">
-        <v>120</v>
-      </c>
-      <c r="B119" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C119" s="5" t="s">
-        <v>388</v>
-      </c>
+      <c r="A119" s="5"/>
+      <c r="B119" s="6"/>
+      <c r="C119" s="5"/>
       <c r="D119" s="4"/>
     </row>
     <row r="120" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A120" s="5" t="s">
-        <v>121</v>
-      </c>
-      <c r="B120" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C120" s="5" t="s">
-        <v>389</v>
-      </c>
+      <c r="A120" s="5"/>
+      <c r="B120" s="6"/>
+      <c r="C120" s="5"/>
       <c r="D120" s="4"/>
     </row>
     <row r="121" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A121" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="B121" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C121" s="5" t="s">
-        <v>390</v>
-      </c>
+      <c r="A121" s="5"/>
+      <c r="B121" s="6"/>
+      <c r="C121" s="5"/>
       <c r="D121" s="4"/>
     </row>
     <row r="122" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A122" s="5" t="s">
-        <v>123</v>
-      </c>
-      <c r="B122" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C122" s="5" t="s">
-        <v>391</v>
-      </c>
+      <c r="A122" s="5"/>
+      <c r="B122" s="6"/>
+      <c r="C122" s="5"/>
       <c r="D122" s="4"/>
     </row>
     <row r="123" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A123" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="B123" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C123" s="5" t="s">
-        <v>392</v>
-      </c>
+      <c r="A123" s="5"/>
+      <c r="B123" s="6"/>
+      <c r="C123" s="5"/>
       <c r="D123" s="4"/>
     </row>
     <row r="124" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A124" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="B124" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C124" s="7" t="s">
-        <v>393</v>
-      </c>
+      <c r="A124" s="5"/>
+      <c r="B124" s="6"/>
+      <c r="C124" s="7"/>
       <c r="D124" s="4"/>
     </row>
     <row r="125" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A125" s="5" t="s">
-        <v>126</v>
-      </c>
-      <c r="B125" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C125" s="5" t="s">
-        <v>394</v>
-      </c>
+      <c r="A125" s="5"/>
+      <c r="B125" s="6"/>
+      <c r="C125" s="5"/>
       <c r="D125" s="4"/>
     </row>
     <row r="126" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A126" s="5" t="s">
-        <v>127</v>
-      </c>
-      <c r="B126" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C126" s="5" t="s">
-        <v>395</v>
-      </c>
+      <c r="A126" s="5"/>
+      <c r="B126" s="6"/>
+      <c r="C126" s="5"/>
       <c r="D126" s="4"/>
     </row>
     <row r="127" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A127" s="5" t="s">
-        <v>128</v>
-      </c>
-      <c r="B127" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C127" s="5" t="s">
-        <v>396</v>
-      </c>
+      <c r="A127" s="5"/>
+      <c r="B127" s="6"/>
+      <c r="C127" s="5"/>
       <c r="D127" s="4"/>
     </row>
     <row r="128" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A128" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="B128" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C128" s="5" t="s">
-        <v>397</v>
-      </c>
+      <c r="A128" s="5"/>
+      <c r="B128" s="6"/>
+      <c r="C128" s="5"/>
       <c r="D128" s="4"/>
     </row>
     <row r="129" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A129" s="5" t="s">
-        <v>130</v>
-      </c>
-      <c r="B129" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C129" s="5" t="s">
-        <v>398</v>
-      </c>
+      <c r="A129" s="5"/>
+      <c r="B129" s="6"/>
+      <c r="C129" s="5"/>
       <c r="D129" s="4"/>
     </row>
     <row r="130" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A130" s="5" t="s">
-        <v>131</v>
-      </c>
-      <c r="B130" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C130" s="5" t="s">
-        <v>399</v>
-      </c>
+      <c r="A130" s="5"/>
+      <c r="B130" s="6"/>
+      <c r="C130" s="5"/>
       <c r="D130" s="4"/>
     </row>
     <row r="131" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A131" s="5" t="s">
-        <v>132</v>
-      </c>
-      <c r="B131" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C131" s="5" t="s">
-        <v>400</v>
-      </c>
+      <c r="A131" s="5"/>
+      <c r="B131" s="6"/>
+      <c r="C131" s="5"/>
       <c r="D131" s="4"/>
     </row>
     <row r="132" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A132" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="B132" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C132" s="5" t="s">
-        <v>401</v>
-      </c>
+      <c r="A132" s="5"/>
+      <c r="B132" s="6"/>
+      <c r="C132" s="5"/>
       <c r="D132" s="4"/>
     </row>
     <row r="133" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A133" s="5" t="s">
-        <v>134</v>
-      </c>
-      <c r="B133" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C133" s="5" t="s">
-        <v>402</v>
-      </c>
+      <c r="A133" s="5"/>
+      <c r="B133" s="6"/>
+      <c r="C133" s="5"/>
       <c r="D133" s="4"/>
     </row>
     <row r="134" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A134" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="B134" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C134" s="5" t="s">
-        <v>403</v>
-      </c>
+      <c r="A134" s="5"/>
+      <c r="B134" s="6"/>
+      <c r="C134" s="5"/>
       <c r="D134" s="4"/>
     </row>
     <row r="135" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A135" s="5" t="s">
-        <v>136</v>
-      </c>
-      <c r="B135" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C135" s="5" t="s">
-        <v>404</v>
-      </c>
+      <c r="A135" s="5"/>
+      <c r="B135" s="6"/>
+      <c r="C135" s="5"/>
       <c r="D135" s="4"/>
     </row>
     <row r="136" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A136" s="5" t="s">
-        <v>137</v>
-      </c>
-      <c r="B136" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C136" s="5" t="s">
-        <v>405</v>
-      </c>
+      <c r="A136" s="5"/>
+      <c r="B136" s="6"/>
+      <c r="C136" s="5"/>
       <c r="D136" s="4"/>
     </row>
     <row r="137" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A137" s="5" t="s">
-        <v>138</v>
-      </c>
-      <c r="B137" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C137" s="5" t="s">
-        <v>406</v>
-      </c>
+      <c r="A137" s="5"/>
+      <c r="B137" s="6"/>
+      <c r="C137" s="5"/>
       <c r="D137" s="4"/>
     </row>
     <row r="138" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A138" s="5" t="s">
-        <v>139</v>
-      </c>
-      <c r="B138" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C138" s="5" t="s">
-        <v>407</v>
-      </c>
+      <c r="A138" s="5"/>
+      <c r="B138" s="6"/>
+      <c r="C138" s="5"/>
       <c r="D138" s="4"/>
     </row>
     <row r="139" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A139" s="5" t="s">
-        <v>140</v>
-      </c>
-      <c r="B139" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C139" s="5" t="s">
-        <v>408</v>
-      </c>
+      <c r="A139" s="5"/>
+      <c r="B139" s="6"/>
+      <c r="C139" s="5"/>
       <c r="D139" s="4"/>
     </row>
     <row r="140" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A140" s="5" t="s">
-        <v>141</v>
-      </c>
-      <c r="B140" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C140" s="5" t="s">
-        <v>409</v>
-      </c>
+      <c r="A140" s="5"/>
+      <c r="B140" s="6"/>
+      <c r="C140" s="5"/>
       <c r="D140" s="4"/>
     </row>
     <row r="141" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A141" s="5" t="s">
-        <v>142</v>
-      </c>
-      <c r="B141" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C141" s="5" t="s">
-        <v>410</v>
-      </c>
+      <c r="A141" s="5"/>
+      <c r="B141" s="6"/>
+      <c r="C141" s="5"/>
       <c r="D141" s="4"/>
     </row>
     <row r="142" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A142" s="5" t="s">
-        <v>143</v>
-      </c>
-      <c r="B142" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C142" s="5" t="s">
-        <v>411</v>
-      </c>
+      <c r="A142" s="5"/>
+      <c r="B142" s="6"/>
+      <c r="C142" s="5"/>
       <c r="D142" s="4"/>
     </row>
     <row r="143" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A143" s="5" t="s">
-        <v>144</v>
-      </c>
-      <c r="B143" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C143" s="5" t="s">
-        <v>412</v>
-      </c>
+      <c r="A143" s="5"/>
+      <c r="B143" s="6"/>
+      <c r="C143" s="5"/>
       <c r="D143" s="4"/>
     </row>
     <row r="144" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A144" s="5" t="s">
-        <v>145</v>
-      </c>
-      <c r="B144" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C144" s="5" t="s">
-        <v>413</v>
-      </c>
+      <c r="A144" s="5"/>
+      <c r="B144" s="6"/>
+      <c r="C144" s="5"/>
       <c r="D144" s="4"/>
     </row>
     <row r="145" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A145" s="5" t="s">
-        <v>146</v>
-      </c>
-      <c r="B145" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C145" s="5" t="s">
-        <v>414</v>
-      </c>
+      <c r="A145" s="5"/>
+      <c r="B145" s="6"/>
+      <c r="C145" s="5"/>
       <c r="D145" s="4"/>
     </row>
     <row r="146" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A146" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="B146" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C146" s="5" t="s">
-        <v>415</v>
-      </c>
+      <c r="A146" s="5"/>
+      <c r="B146" s="6"/>
+      <c r="C146" s="5"/>
       <c r="D146" s="4"/>
     </row>
     <row r="147" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A147" s="5" t="s">
-        <v>148</v>
-      </c>
-      <c r="B147" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C147" s="5" t="s">
-        <v>416</v>
-      </c>
+      <c r="A147" s="5"/>
+      <c r="B147" s="6"/>
+      <c r="C147" s="5"/>
       <c r="D147" s="4"/>
     </row>
     <row r="148" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A148" s="5" t="s">
-        <v>149</v>
-      </c>
-      <c r="B148" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C148" s="5" t="s">
-        <v>417</v>
-      </c>
+      <c r="A148" s="5"/>
+      <c r="B148" s="6"/>
+      <c r="C148" s="5"/>
       <c r="D148" s="4"/>
     </row>
     <row r="149" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A149" s="5" t="s">
-        <v>150</v>
-      </c>
-      <c r="B149" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C149" s="5" t="s">
-        <v>418</v>
-      </c>
+      <c r="A149" s="5"/>
+      <c r="B149" s="6"/>
+      <c r="C149" s="5"/>
       <c r="D149" s="4"/>
     </row>
     <row r="150" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A150" s="5" t="s">
-        <v>151</v>
-      </c>
-      <c r="B150" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C150" s="5" t="s">
-        <v>419</v>
-      </c>
+      <c r="A150" s="5"/>
+      <c r="B150" s="6"/>
+      <c r="C150" s="5"/>
       <c r="D150" s="4"/>
     </row>
     <row r="151" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A151" s="5" t="s">
-        <v>152</v>
-      </c>
-      <c r="B151" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C151" s="5" t="s">
-        <v>420</v>
-      </c>
+      <c r="A151" s="5"/>
+      <c r="B151" s="6"/>
+      <c r="C151" s="5"/>
       <c r="D151" s="4"/>
     </row>
     <row r="152" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A152" s="5" t="s">
-        <v>153</v>
-      </c>
-      <c r="B152" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C152" s="5" t="s">
-        <v>421</v>
-      </c>
+      <c r="A152" s="5"/>
+      <c r="B152" s="6"/>
+      <c r="C152" s="5"/>
       <c r="D152" s="4"/>
     </row>
     <row r="153" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A153" s="5" t="s">
-        <v>154</v>
-      </c>
-      <c r="B153" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C153" s="5" t="s">
-        <v>422</v>
-      </c>
+      <c r="A153" s="5"/>
+      <c r="B153" s="6"/>
+      <c r="C153" s="5"/>
       <c r="D153" s="4"/>
     </row>
     <row r="154" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A154" s="5" t="s">
-        <v>155</v>
-      </c>
-      <c r="B154" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C154" s="5" t="s">
-        <v>423</v>
-      </c>
+      <c r="A154" s="5"/>
+      <c r="B154" s="6"/>
+      <c r="C154" s="5"/>
       <c r="D154" s="4"/>
     </row>
     <row r="155" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A155" s="5" t="s">
-        <v>156</v>
-      </c>
-      <c r="B155" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C155" s="5" t="s">
-        <v>424</v>
-      </c>
+      <c r="A155" s="5"/>
+      <c r="B155" s="6"/>
+      <c r="C155" s="5"/>
       <c r="D155" s="4"/>
     </row>
     <row r="156" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A156" s="5" t="s">
-        <v>157</v>
-      </c>
-      <c r="B156" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C156" s="5" t="s">
-        <v>425</v>
-      </c>
+      <c r="A156" s="5"/>
+      <c r="B156" s="6"/>
+      <c r="C156" s="5"/>
       <c r="D156" s="4"/>
     </row>
     <row r="157" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A157" s="5" t="s">
-        <v>158</v>
-      </c>
-      <c r="B157" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C157" s="5" t="s">
-        <v>426</v>
-      </c>
+      <c r="A157" s="5"/>
+      <c r="B157" s="6"/>
+      <c r="C157" s="5"/>
       <c r="D157" s="4"/>
     </row>
     <row r="158" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A158" s="5" t="s">
-        <v>159</v>
-      </c>
-      <c r="B158" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C158" s="5" t="s">
-        <v>427</v>
-      </c>
+      <c r="A158" s="5"/>
+      <c r="B158" s="6"/>
+      <c r="C158" s="5"/>
       <c r="D158" s="4"/>
     </row>
     <row r="159" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A159" s="5" t="s">
-        <v>160</v>
-      </c>
-      <c r="B159" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C159" s="5" t="s">
-        <v>428</v>
-      </c>
+      <c r="A159" s="5"/>
+      <c r="B159" s="6"/>
+      <c r="C159" s="5"/>
       <c r="D159" s="4"/>
     </row>
     <row r="160" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A160" s="5" t="s">
-        <v>161</v>
-      </c>
-      <c r="B160" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C160" s="5" t="s">
-        <v>429</v>
-      </c>
+      <c r="A160" s="5"/>
+      <c r="B160" s="6"/>
+      <c r="C160" s="5"/>
       <c r="D160" s="4"/>
     </row>
     <row r="161" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A161" s="5" t="s">
-        <v>162</v>
-      </c>
-      <c r="B161" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C161" s="5" t="s">
-        <v>430</v>
-      </c>
+      <c r="A161" s="5"/>
+      <c r="B161" s="6"/>
+      <c r="C161" s="5"/>
       <c r="D161" s="4"/>
     </row>
     <row r="162" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A162" s="5" t="s">
-        <v>163</v>
-      </c>
-      <c r="B162" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C162" s="5" t="s">
-        <v>431</v>
-      </c>
+      <c r="A162" s="5"/>
+      <c r="B162" s="6"/>
+      <c r="C162" s="5"/>
       <c r="D162" s="4"/>
     </row>
     <row r="163" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A163" s="5" t="s">
-        <v>164</v>
-      </c>
-      <c r="B163" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C163" s="5" t="s">
-        <v>432</v>
-      </c>
+      <c r="A163" s="5"/>
+      <c r="B163" s="6"/>
+      <c r="C163" s="5"/>
       <c r="D163" s="4"/>
     </row>
     <row r="164" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A164" s="5" t="s">
-        <v>165</v>
-      </c>
-      <c r="B164" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C164" s="5" t="s">
-        <v>433</v>
-      </c>
+      <c r="A164" s="5"/>
+      <c r="B164" s="6"/>
+      <c r="C164" s="5"/>
       <c r="D164" s="4"/>
     </row>
     <row r="165" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A165" s="5" t="s">
-        <v>166</v>
-      </c>
-      <c r="B165" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C165" s="5" t="s">
-        <v>434</v>
-      </c>
+      <c r="A165" s="5"/>
+      <c r="B165" s="6"/>
+      <c r="C165" s="5"/>
       <c r="D165" s="4"/>
     </row>
     <row r="166" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A166" s="5" t="s">
-        <v>167</v>
-      </c>
-      <c r="B166" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C166" s="5" t="s">
-        <v>435</v>
-      </c>
+      <c r="A166" s="5"/>
+      <c r="B166" s="6"/>
+      <c r="C166" s="5"/>
       <c r="D166" s="4"/>
     </row>
     <row r="167" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A167" s="5" t="s">
-        <v>168</v>
-      </c>
-      <c r="B167" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C167" s="5" t="s">
-        <v>436</v>
-      </c>
+      <c r="A167" s="5"/>
+      <c r="B167" s="6"/>
+      <c r="C167" s="5"/>
       <c r="D167" s="4"/>
     </row>
     <row r="168" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A168" s="5" t="s">
-        <v>169</v>
-      </c>
-      <c r="B168" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C168" s="5" t="s">
-        <v>437</v>
-      </c>
+      <c r="A168" s="5"/>
+      <c r="B168" s="6"/>
+      <c r="C168" s="5"/>
       <c r="D168" s="4"/>
     </row>
     <row r="169" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A169" s="5" t="s">
-        <v>170</v>
-      </c>
-      <c r="B169" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C169" s="5" t="s">
-        <v>438</v>
-      </c>
+      <c r="A169" s="5"/>
+      <c r="B169" s="6"/>
+      <c r="C169" s="5"/>
       <c r="D169" s="4"/>
     </row>
     <row r="170" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A170" s="5" t="s">
-        <v>171</v>
-      </c>
-      <c r="B170" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C170" s="5" t="s">
-        <v>439</v>
-      </c>
+      <c r="A170" s="5"/>
+      <c r="B170" s="6"/>
+      <c r="C170" s="5"/>
       <c r="D170" s="4"/>
     </row>
     <row r="171" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A171" s="5" t="s">
-        <v>172</v>
-      </c>
-      <c r="B171" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C171" s="5" t="s">
-        <v>440</v>
-      </c>
+      <c r="A171" s="5"/>
+      <c r="B171" s="6"/>
+      <c r="C171" s="5"/>
       <c r="D171" s="4"/>
     </row>
     <row r="172" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A172" s="5" t="s">
-        <v>173</v>
-      </c>
-      <c r="B172" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C172" s="5" t="s">
-        <v>441</v>
-      </c>
+      <c r="A172" s="5"/>
+      <c r="B172" s="6"/>
+      <c r="C172" s="5"/>
       <c r="D172" s="4"/>
     </row>
     <row r="173" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A173" s="5" t="s">
-        <v>174</v>
-      </c>
-      <c r="B173" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C173" s="5" t="s">
-        <v>442</v>
-      </c>
+      <c r="A173" s="5"/>
+      <c r="B173" s="6"/>
+      <c r="C173" s="5"/>
       <c r="D173" s="4"/>
     </row>
     <row r="174" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A174" s="5" t="s">
-        <v>175</v>
-      </c>
-      <c r="B174" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C174" s="5" t="s">
-        <v>443</v>
-      </c>
+      <c r="A174" s="5"/>
+      <c r="B174" s="6"/>
+      <c r="C174" s="5"/>
       <c r="D174" s="4"/>
     </row>
     <row r="175" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A175" s="5" t="s">
-        <v>176</v>
-      </c>
-      <c r="B175" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C175" s="5" t="s">
-        <v>444</v>
-      </c>
+      <c r="A175" s="5"/>
+      <c r="B175" s="6"/>
+      <c r="C175" s="5"/>
       <c r="D175" s="4"/>
     </row>
     <row r="176" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A176" s="5" t="s">
-        <v>177</v>
-      </c>
-      <c r="B176" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C176" s="5" t="s">
-        <v>445</v>
-      </c>
+      <c r="A176" s="5"/>
+      <c r="B176" s="6"/>
+      <c r="C176" s="5"/>
       <c r="D176" s="4"/>
     </row>
     <row r="177" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A177" s="5" t="s">
-        <v>178</v>
-      </c>
-      <c r="B177" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C177" s="5" t="s">
-        <v>446</v>
-      </c>
+      <c r="A177" s="5"/>
+      <c r="B177" s="6"/>
+      <c r="C177" s="5"/>
       <c r="D177" s="4"/>
     </row>
     <row r="178" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A178" s="5" t="s">
-        <v>179</v>
-      </c>
-      <c r="B178" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C178" s="5" t="s">
-        <v>447</v>
-      </c>
+      <c r="A178" s="5"/>
+      <c r="B178" s="6"/>
+      <c r="C178" s="5"/>
       <c r="D178" s="4"/>
     </row>
     <row r="179" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A179" s="5" t="s">
-        <v>180</v>
-      </c>
-      <c r="B179" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C179" s="5" t="s">
-        <v>448</v>
-      </c>
+      <c r="A179" s="5"/>
+      <c r="B179" s="6"/>
+      <c r="C179" s="5"/>
       <c r="D179" s="4"/>
     </row>
     <row r="180" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A180" s="5" t="s">
-        <v>181</v>
-      </c>
-      <c r="B180" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C180" s="5" t="s">
-        <v>449</v>
-      </c>
+      <c r="A180" s="5"/>
+      <c r="B180" s="6"/>
+      <c r="C180" s="5"/>
       <c r="D180" s="4"/>
     </row>
     <row r="181" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A181" s="5" t="s">
-        <v>182</v>
-      </c>
-      <c r="B181" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C181" s="5" t="s">
-        <v>450</v>
-      </c>
+      <c r="A181" s="5"/>
+      <c r="B181" s="6"/>
+      <c r="C181" s="5"/>
       <c r="D181" s="4"/>
     </row>
     <row r="182" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A182" s="5" t="s">
-        <v>183</v>
-      </c>
-      <c r="B182" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C182" s="5" t="s">
-        <v>451</v>
-      </c>
+      <c r="A182" s="5"/>
+      <c r="B182" s="6"/>
+      <c r="C182" s="5"/>
       <c r="D182" s="4"/>
     </row>
     <row r="183" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A183" s="5" t="s">
-        <v>184</v>
-      </c>
-      <c r="B183" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C183" s="5" t="s">
-        <v>452</v>
-      </c>
+      <c r="A183" s="5"/>
+      <c r="B183" s="6"/>
+      <c r="C183" s="5"/>
       <c r="D183" s="4"/>
     </row>
     <row r="184" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A184" s="5" t="s">
-        <v>185</v>
-      </c>
-      <c r="B184" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C184" s="5" t="s">
-        <v>453</v>
-      </c>
+      <c r="A184" s="5"/>
+      <c r="B184" s="6"/>
+      <c r="C184" s="5"/>
       <c r="D184" s="4"/>
     </row>
     <row r="185" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A185" s="5" t="s">
-        <v>186</v>
-      </c>
-      <c r="B185" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C185" s="5" t="s">
-        <v>454</v>
-      </c>
+      <c r="A185" s="5"/>
+      <c r="B185" s="6"/>
+      <c r="C185" s="5"/>
       <c r="D185" s="4"/>
     </row>
     <row r="186" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A186" s="5" t="s">
-        <v>187</v>
-      </c>
-      <c r="B186" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C186" s="5" t="s">
-        <v>455</v>
-      </c>
+      <c r="A186" s="5"/>
+      <c r="B186" s="6"/>
+      <c r="C186" s="5"/>
       <c r="D186" s="4"/>
     </row>
     <row r="187" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A187" s="5" t="s">
-        <v>188</v>
-      </c>
-      <c r="B187" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C187" s="5" t="s">
-        <v>456</v>
-      </c>
+      <c r="A187" s="5"/>
+      <c r="B187" s="6"/>
+      <c r="C187" s="5"/>
       <c r="D187" s="4"/>
     </row>
     <row r="188" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A188" s="5" t="s">
-        <v>189</v>
-      </c>
-      <c r="B188" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C188" s="5" t="s">
-        <v>457</v>
-      </c>
+      <c r="A188" s="5"/>
+      <c r="B188" s="6"/>
+      <c r="C188" s="5"/>
       <c r="D188" s="4"/>
     </row>
     <row r="189" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A189" s="5" t="s">
-        <v>190</v>
-      </c>
-      <c r="B189" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C189" s="5" t="s">
-        <v>458</v>
-      </c>
+      <c r="A189" s="5"/>
+      <c r="B189" s="6"/>
+      <c r="C189" s="5"/>
       <c r="D189" s="4"/>
     </row>
     <row r="190" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A190" s="5" t="s">
-        <v>191</v>
-      </c>
-      <c r="B190" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C190" s="5" t="s">
-        <v>459</v>
-      </c>
+      <c r="A190" s="5"/>
+      <c r="B190" s="6"/>
+      <c r="C190" s="5"/>
       <c r="D190" s="4"/>
     </row>
     <row r="191" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A191" s="5" t="s">
-        <v>192</v>
-      </c>
-      <c r="B191" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C191" s="5" t="s">
-        <v>460</v>
-      </c>
+      <c r="A191" s="5"/>
+      <c r="B191" s="6"/>
+      <c r="C191" s="5"/>
       <c r="D191" s="4"/>
     </row>
     <row r="192" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A192" s="5" t="s">
-        <v>193</v>
-      </c>
-      <c r="B192" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C192" s="5" t="s">
-        <v>461</v>
-      </c>
+      <c r="A192" s="5"/>
+      <c r="B192" s="6"/>
+      <c r="C192" s="5"/>
       <c r="D192" s="4"/>
     </row>
     <row r="193" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A193" s="5" t="s">
-        <v>194</v>
-      </c>
-      <c r="B193" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C193" s="5" t="s">
-        <v>462</v>
-      </c>
+      <c r="A193" s="5"/>
+      <c r="B193" s="6"/>
+      <c r="C193" s="5"/>
       <c r="D193" s="4"/>
     </row>
     <row r="194" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A194" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="B194" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C194" s="5" t="s">
-        <v>463</v>
-      </c>
+      <c r="A194" s="5"/>
+      <c r="B194" s="6"/>
+      <c r="C194" s="5"/>
       <c r="D194" s="4"/>
     </row>
     <row r="195" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A195" s="5" t="s">
-        <v>196</v>
-      </c>
-      <c r="B195" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C195" s="5" t="s">
-        <v>464</v>
-      </c>
+      <c r="A195" s="5"/>
+      <c r="B195" s="6"/>
+      <c r="C195" s="5"/>
       <c r="D195" s="4"/>
     </row>
     <row r="196" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A196" s="5" t="s">
-        <v>197</v>
-      </c>
-      <c r="B196" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C196" s="5" t="s">
-        <v>465</v>
-      </c>
+      <c r="A196" s="5"/>
+      <c r="B196" s="6"/>
+      <c r="C196" s="5"/>
       <c r="D196" s="4"/>
     </row>
     <row r="197" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A197" s="5" t="s">
-        <v>198</v>
-      </c>
-      <c r="B197" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C197" s="5" t="s">
-        <v>466</v>
-      </c>
+      <c r="A197" s="5"/>
+      <c r="B197" s="6"/>
+      <c r="C197" s="5"/>
       <c r="D197" s="4"/>
     </row>
     <row r="198" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A198" s="5" t="s">
-        <v>199</v>
-      </c>
-      <c r="B198" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C198" s="5" t="s">
-        <v>467</v>
-      </c>
+      <c r="A198" s="5"/>
+      <c r="B198" s="6"/>
+      <c r="C198" s="5"/>
       <c r="D198" s="4"/>
     </row>
     <row r="199" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A199" s="5" t="s">
-        <v>200</v>
-      </c>
-      <c r="B199" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C199" s="5" t="s">
-        <v>468</v>
-      </c>
+      <c r="A199" s="5"/>
+      <c r="B199" s="6"/>
+      <c r="C199" s="5"/>
       <c r="D199" s="4"/>
     </row>
     <row r="200" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A200" s="5" t="s">
-        <v>201</v>
-      </c>
-      <c r="B200" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C200" s="5" t="s">
-        <v>469</v>
-      </c>
+      <c r="A200" s="5"/>
+      <c r="B200" s="6"/>
+      <c r="C200" s="5"/>
       <c r="D200" s="4"/>
     </row>
     <row r="201" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A201" s="5" t="s">
-        <v>202</v>
-      </c>
-      <c r="B201" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C201" s="5" t="s">
-        <v>470</v>
-      </c>
+      <c r="A201" s="5"/>
+      <c r="B201" s="6"/>
+      <c r="C201" s="5"/>
       <c r="D201" s="4"/>
     </row>
     <row r="202" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A202" s="5" t="s">
-        <v>203</v>
-      </c>
-      <c r="B202" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C202" s="5" t="s">
-        <v>471</v>
-      </c>
+      <c r="A202" s="5"/>
+      <c r="B202" s="6"/>
+      <c r="C202" s="5"/>
       <c r="D202" s="4"/>
     </row>
     <row r="203" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A203" s="5" t="s">
-        <v>204</v>
-      </c>
-      <c r="B203" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C203" s="5" t="s">
-        <v>472</v>
-      </c>
+      <c r="A203" s="5"/>
+      <c r="B203" s="6"/>
+      <c r="C203" s="5"/>
       <c r="D203" s="4"/>
     </row>
     <row r="204" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A204" s="5" t="s">
-        <v>205</v>
-      </c>
-      <c r="B204" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C204" s="5" t="s">
-        <v>473</v>
-      </c>
+      <c r="A204" s="5"/>
+      <c r="B204" s="6"/>
+      <c r="C204" s="5"/>
       <c r="D204" s="4"/>
     </row>
     <row r="205" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A205" s="5" t="s">
-        <v>206</v>
-      </c>
-      <c r="B205" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C205" s="5" t="s">
-        <v>474</v>
-      </c>
+      <c r="A205" s="5"/>
+      <c r="B205" s="6"/>
+      <c r="C205" s="5"/>
       <c r="D205" s="4"/>
     </row>
     <row r="206" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A206" s="5" t="s">
-        <v>207</v>
-      </c>
-      <c r="B206" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C206" s="5" t="s">
-        <v>475</v>
-      </c>
+      <c r="A206" s="5"/>
+      <c r="B206" s="6"/>
+      <c r="C206" s="5"/>
       <c r="D206" s="4"/>
     </row>
     <row r="207" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A207" s="5" t="s">
-        <v>208</v>
-      </c>
-      <c r="B207" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C207" s="5" t="s">
-        <v>476</v>
-      </c>
+      <c r="A207" s="5"/>
+      <c r="B207" s="6"/>
+      <c r="C207" s="5"/>
       <c r="D207" s="4"/>
     </row>
     <row r="208" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A208" s="5" t="s">
-        <v>209</v>
-      </c>
-      <c r="B208" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C208" s="5" t="s">
-        <v>477</v>
-      </c>
+      <c r="A208" s="5"/>
+      <c r="B208" s="6"/>
+      <c r="C208" s="5"/>
       <c r="D208" s="4"/>
     </row>
     <row r="209" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A209" s="5" t="s">
-        <v>210</v>
-      </c>
-      <c r="B209" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C209" s="5" t="s">
-        <v>478</v>
-      </c>
+      <c r="A209" s="5"/>
+      <c r="B209" s="6"/>
+      <c r="C209" s="5"/>
       <c r="D209" s="4"/>
     </row>
     <row r="210" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A210" s="5" t="s">
-        <v>211</v>
-      </c>
-      <c r="B210" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C210" s="5" t="s">
-        <v>479</v>
-      </c>
+      <c r="A210" s="5"/>
+      <c r="B210" s="6"/>
+      <c r="C210" s="5"/>
       <c r="D210" s="4"/>
     </row>
     <row r="211" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A211" s="5" t="s">
-        <v>212</v>
-      </c>
-      <c r="B211" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C211" s="5" t="s">
-        <v>480</v>
-      </c>
+      <c r="A211" s="5"/>
+      <c r="B211" s="6"/>
+      <c r="C211" s="5"/>
       <c r="D211" s="4"/>
     </row>
     <row r="212" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A212" s="5" t="s">
-        <v>213</v>
-      </c>
-      <c r="B212" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C212" s="5" t="s">
-        <v>481</v>
-      </c>
+      <c r="A212" s="5"/>
+      <c r="B212" s="6"/>
+      <c r="C212" s="5"/>
       <c r="D212" s="4"/>
     </row>
     <row r="213" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A213" s="5" t="s">
-        <v>214</v>
-      </c>
-      <c r="B213" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C213" s="5" t="s">
-        <v>482</v>
-      </c>
+      <c r="A213" s="5"/>
+      <c r="B213" s="6"/>
+      <c r="C213" s="5"/>
       <c r="D213" s="4"/>
     </row>
     <row r="214" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A214" s="5" t="s">
-        <v>215</v>
-      </c>
-      <c r="B214" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C214" s="5" t="s">
-        <v>483</v>
-      </c>
+      <c r="A214" s="5"/>
+      <c r="B214" s="6"/>
+      <c r="C214" s="5"/>
       <c r="D214" s="4"/>
     </row>
     <row r="215" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A215" s="5" t="s">
-        <v>216</v>
-      </c>
-      <c r="B215" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C215" s="5" t="s">
-        <v>484</v>
-      </c>
+      <c r="A215" s="5"/>
+      <c r="B215" s="6"/>
+      <c r="C215" s="5"/>
       <c r="D215" s="4"/>
     </row>
     <row r="216" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A216" s="5" t="s">
-        <v>217</v>
-      </c>
-      <c r="B216" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C216" s="5" t="s">
-        <v>485</v>
-      </c>
+      <c r="A216" s="5"/>
+      <c r="B216" s="6"/>
+      <c r="C216" s="5"/>
       <c r="D216" s="4"/>
     </row>
     <row r="217" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A217" s="5" t="s">
-        <v>218</v>
-      </c>
-      <c r="B217" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C217" s="5" t="s">
-        <v>486</v>
-      </c>
+      <c r="A217" s="5"/>
+      <c r="B217" s="6"/>
+      <c r="C217" s="5"/>
       <c r="D217" s="4"/>
     </row>
     <row r="218" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A218" s="5" t="s">
-        <v>219</v>
-      </c>
-      <c r="B218" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C218" s="5" t="s">
-        <v>487</v>
-      </c>
+      <c r="A218" s="5"/>
+      <c r="B218" s="6"/>
+      <c r="C218" s="5"/>
       <c r="D218" s="4"/>
     </row>
     <row r="219" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A219" s="5" t="s">
-        <v>220</v>
-      </c>
-      <c r="B219" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C219" s="5" t="s">
-        <v>488</v>
-      </c>
+      <c r="A219" s="5"/>
+      <c r="B219" s="6"/>
+      <c r="C219" s="5"/>
       <c r="D219" s="4"/>
     </row>
     <row r="220" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A220" s="5" t="s">
-        <v>221</v>
-      </c>
-      <c r="B220" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C220" s="5" t="s">
-        <v>489</v>
-      </c>
+      <c r="A220" s="5"/>
+      <c r="B220" s="6"/>
+      <c r="C220" s="5"/>
       <c r="D220" s="4"/>
     </row>
     <row r="221" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A221" s="5" t="s">
-        <v>222</v>
-      </c>
-      <c r="B221" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C221" s="5" t="s">
-        <v>490</v>
-      </c>
+      <c r="A221" s="5"/>
+      <c r="B221" s="6"/>
+      <c r="C221" s="5"/>
       <c r="D221" s="4"/>
     </row>
     <row r="222" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A222" s="5" t="s">
-        <v>223</v>
-      </c>
-      <c r="B222" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C222" s="5" t="s">
-        <v>491</v>
-      </c>
+      <c r="A222" s="5"/>
+      <c r="B222" s="6"/>
+      <c r="C222" s="5"/>
       <c r="D222" s="4"/>
     </row>
     <row r="223" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A223" s="5" t="s">
-        <v>224</v>
-      </c>
-      <c r="B223" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C223" s="5" t="s">
-        <v>492</v>
-      </c>
+      <c r="A223" s="5"/>
+      <c r="B223" s="6"/>
+      <c r="C223" s="5"/>
       <c r="D223" s="4"/>
     </row>
     <row r="224" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A224" s="5" t="s">
-        <v>225</v>
-      </c>
-      <c r="B224" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C224" s="5" t="s">
-        <v>493</v>
-      </c>
+      <c r="A224" s="5"/>
+      <c r="B224" s="6"/>
+      <c r="C224" s="5"/>
       <c r="D224" s="4"/>
     </row>
     <row r="225" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A225" s="5" t="s">
-        <v>226</v>
-      </c>
-      <c r="B225" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C225" s="5" t="s">
-        <v>494</v>
-      </c>
+      <c r="A225" s="5"/>
+      <c r="B225" s="6"/>
+      <c r="C225" s="5"/>
       <c r="D225" s="4"/>
     </row>
     <row r="226" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A226" s="5" t="s">
-        <v>227</v>
-      </c>
-      <c r="B226" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C226" s="5" t="s">
-        <v>495</v>
-      </c>
+      <c r="A226" s="5"/>
+      <c r="B226" s="6"/>
+      <c r="C226" s="5"/>
       <c r="D226" s="4"/>
     </row>
     <row r="227" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A227" s="5" t="s">
-        <v>228</v>
-      </c>
-      <c r="B227" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C227" s="5" t="s">
-        <v>496</v>
-      </c>
+      <c r="A227" s="5"/>
+      <c r="B227" s="6"/>
+      <c r="C227" s="5"/>
       <c r="D227" s="4"/>
     </row>
     <row r="228" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A228" s="5" t="s">
-        <v>229</v>
-      </c>
-      <c r="B228" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C228" s="5" t="s">
-        <v>497</v>
-      </c>
+      <c r="A228" s="5"/>
+      <c r="B228" s="6"/>
+      <c r="C228" s="5"/>
       <c r="D228" s="4"/>
     </row>
     <row r="229" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A229" s="5" t="s">
-        <v>230</v>
-      </c>
-      <c r="B229" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C229" s="5" t="s">
-        <v>498</v>
-      </c>
+      <c r="A229" s="5"/>
+      <c r="B229" s="6"/>
+      <c r="C229" s="5"/>
       <c r="D229" s="4"/>
     </row>
     <row r="230" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A230" s="5" t="s">
-        <v>231</v>
-      </c>
-      <c r="B230" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C230" s="5" t="s">
-        <v>499</v>
-      </c>
+      <c r="A230" s="5"/>
+      <c r="B230" s="6"/>
+      <c r="C230" s="5"/>
       <c r="D230" s="4"/>
     </row>
     <row r="231" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A231" s="5" t="s">
-        <v>232</v>
-      </c>
-      <c r="B231" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C231" s="5" t="s">
-        <v>500</v>
-      </c>
+      <c r="A231" s="5"/>
+      <c r="B231" s="6"/>
+      <c r="C231" s="5"/>
       <c r="D231" s="4"/>
     </row>
     <row r="232" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A232" s="5" t="s">
-        <v>233</v>
-      </c>
-      <c r="B232" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C232" s="5" t="s">
-        <v>501</v>
-      </c>
+      <c r="A232" s="5"/>
+      <c r="B232" s="6"/>
+      <c r="C232" s="5"/>
       <c r="D232" s="4"/>
     </row>
     <row r="233" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A233" s="5" t="s">
-        <v>234</v>
-      </c>
-      <c r="B233" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C233" s="5" t="s">
-        <v>502</v>
-      </c>
+      <c r="A233" s="5"/>
+      <c r="B233" s="6"/>
+      <c r="C233" s="5"/>
       <c r="D233" s="4"/>
     </row>
     <row r="234" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A234" s="5" t="s">
-        <v>235</v>
-      </c>
-      <c r="B234" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C234" s="5" t="s">
-        <v>503</v>
-      </c>
+      <c r="A234" s="5"/>
+      <c r="B234" s="6"/>
+      <c r="C234" s="5"/>
       <c r="D234" s="4"/>
     </row>
     <row r="235" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A235" s="5" t="s">
-        <v>236</v>
-      </c>
-      <c r="B235" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C235" s="5" t="s">
-        <v>504</v>
-      </c>
+      <c r="A235" s="5"/>
+      <c r="B235" s="6"/>
+      <c r="C235" s="5"/>
       <c r="D235" s="4"/>
     </row>
     <row r="236" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A236" s="5" t="s">
-        <v>237</v>
-      </c>
-      <c r="B236" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C236" s="5" t="s">
-        <v>505</v>
-      </c>
+      <c r="A236" s="5"/>
+      <c r="B236" s="6"/>
+      <c r="C236" s="5"/>
       <c r="D236" s="4"/>
     </row>
     <row r="237" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A237" s="5" t="s">
-        <v>238</v>
-      </c>
-      <c r="B237" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C237" s="5" t="s">
-        <v>506</v>
-      </c>
+      <c r="A237" s="5"/>
+      <c r="B237" s="6"/>
+      <c r="C237" s="5"/>
       <c r="D237" s="4"/>
     </row>
     <row r="238" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A238" s="5" t="s">
-        <v>239</v>
-      </c>
-      <c r="B238" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C238" s="5" t="s">
-        <v>507</v>
-      </c>
+      <c r="A238" s="5"/>
+      <c r="B238" s="6"/>
+      <c r="C238" s="5"/>
       <c r="D238" s="4"/>
     </row>
     <row r="239" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A239" s="5" t="s">
-        <v>240</v>
-      </c>
-      <c r="B239" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C239" s="5" t="s">
-        <v>508</v>
-      </c>
+      <c r="A239" s="5"/>
+      <c r="B239" s="6"/>
+      <c r="C239" s="5"/>
       <c r="D239" s="4"/>
     </row>
     <row r="240" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A240" s="5" t="s">
-        <v>241</v>
-      </c>
-      <c r="B240" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C240" s="5" t="s">
-        <v>509</v>
-      </c>
+      <c r="A240" s="5"/>
+      <c r="B240" s="6"/>
+      <c r="C240" s="5"/>
       <c r="D240" s="4"/>
     </row>
     <row r="241" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A241" s="5" t="s">
-        <v>242</v>
-      </c>
-      <c r="B241" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C241" s="5" t="s">
-        <v>510</v>
-      </c>
+      <c r="A241" s="5"/>
+      <c r="B241" s="6"/>
+      <c r="C241" s="5"/>
       <c r="D241" s="4"/>
     </row>
     <row r="242" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A242" s="5" t="s">
-        <v>243</v>
-      </c>
-      <c r="B242" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C242" s="5" t="s">
-        <v>511</v>
-      </c>
+      <c r="A242" s="5"/>
+      <c r="B242" s="6"/>
+      <c r="C242" s="5"/>
       <c r="D242" s="4"/>
     </row>
     <row r="243" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A243" s="5" t="s">
-        <v>244</v>
-      </c>
-      <c r="B243" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C243" s="5" t="s">
-        <v>512</v>
-      </c>
+      <c r="A243" s="5"/>
+      <c r="B243" s="6"/>
+      <c r="C243" s="5"/>
       <c r="D243" s="4"/>
     </row>
     <row r="244" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A244" s="5" t="s">
-        <v>245</v>
-      </c>
-      <c r="B244" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C244" s="5" t="s">
-        <v>513</v>
-      </c>
+      <c r="A244" s="5"/>
+      <c r="B244" s="6"/>
+      <c r="C244" s="5"/>
       <c r="D244" s="4"/>
     </row>
     <row r="245" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A245" s="5" t="s">
-        <v>246</v>
-      </c>
-      <c r="B245" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C245" s="5" t="s">
-        <v>514</v>
-      </c>
+      <c r="A245" s="5"/>
+      <c r="B245" s="6"/>
+      <c r="C245" s="5"/>
       <c r="D245" s="4"/>
     </row>
     <row r="246" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A246" s="5" t="s">
-        <v>247</v>
-      </c>
-      <c r="B246" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C246" s="5" t="s">
-        <v>515</v>
-      </c>
+      <c r="A246" s="5"/>
+      <c r="B246" s="6"/>
+      <c r="C246" s="5"/>
       <c r="D246" s="4"/>
     </row>
     <row r="247" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A247" s="5" t="s">
-        <v>248</v>
-      </c>
-      <c r="B247" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C247" s="5" t="s">
-        <v>516</v>
-      </c>
+      <c r="A247" s="5"/>
+      <c r="B247" s="6"/>
+      <c r="C247" s="5"/>
       <c r="D247" s="4"/>
     </row>
     <row r="248" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A248" s="5" t="s">
-        <v>249</v>
-      </c>
-      <c r="B248" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C248" s="5" t="s">
-        <v>517</v>
-      </c>
+      <c r="A248" s="5"/>
+      <c r="B248" s="6"/>
+      <c r="C248" s="5"/>
       <c r="D248" s="4"/>
     </row>
     <row r="249" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A249" s="5" t="s">
-        <v>250</v>
-      </c>
-      <c r="B249" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C249" s="5" t="s">
-        <v>402</v>
-      </c>
+      <c r="A249" s="5"/>
+      <c r="B249" s="6"/>
+      <c r="C249" s="5"/>
       <c r="D249" s="4"/>
     </row>
     <row r="250" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A250" s="5" t="s">
-        <v>251</v>
-      </c>
-      <c r="B250" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C250" s="5" t="s">
-        <v>518</v>
-      </c>
+      <c r="A250" s="5"/>
+      <c r="B250" s="6"/>
+      <c r="C250" s="5"/>
       <c r="D250" s="4"/>
     </row>
     <row r="251" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A251" s="5" t="s">
-        <v>252</v>
-      </c>
-      <c r="B251" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C251" s="5" t="s">
-        <v>519</v>
-      </c>
+      <c r="A251" s="5"/>
+      <c r="B251" s="6"/>
+      <c r="C251" s="5"/>
       <c r="D251" s="4"/>
     </row>
     <row r="252" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A252" s="5" t="s">
-        <v>253</v>
-      </c>
-      <c r="B252" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C252" s="5" t="s">
-        <v>520</v>
-      </c>
+      <c r="A252" s="5"/>
+      <c r="B252" s="6"/>
+      <c r="C252" s="5"/>
       <c r="D252" s="4"/>
     </row>
     <row r="253" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A253" s="5" t="s">
-        <v>254</v>
-      </c>
-      <c r="B253" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C253" s="5" t="s">
-        <v>521</v>
-      </c>
+      <c r="A253" s="5"/>
+      <c r="B253" s="6"/>
+      <c r="C253" s="5"/>
       <c r="D253" s="4"/>
     </row>
     <row r="254" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A254" s="5" t="s">
-        <v>255</v>
-      </c>
-      <c r="B254" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C254" s="5" t="s">
-        <v>522</v>
-      </c>
+      <c r="A254" s="5"/>
+      <c r="B254" s="6"/>
+      <c r="C254" s="5"/>
       <c r="D254" s="4"/>
     </row>
     <row r="255" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A255" s="5" t="s">
-        <v>256</v>
-      </c>
-      <c r="B255" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C255" s="5" t="s">
-        <v>523</v>
-      </c>
+      <c r="A255" s="5"/>
+      <c r="B255" s="6"/>
+      <c r="C255" s="5"/>
       <c r="D255" s="4"/>
     </row>
     <row r="256" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A256" s="5" t="s">
-        <v>257</v>
-      </c>
-      <c r="B256" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C256" s="5" t="s">
-        <v>524</v>
-      </c>
+      <c r="A256" s="5"/>
+      <c r="B256" s="6"/>
+      <c r="C256" s="5"/>
       <c r="D256" s="4"/>
     </row>
     <row r="257" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A257" s="5" t="s">
-        <v>258</v>
-      </c>
-      <c r="B257" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C257" s="5" t="s">
-        <v>525</v>
-      </c>
+      <c r="A257" s="5"/>
+      <c r="B257" s="6"/>
+      <c r="C257" s="5"/>
       <c r="D257" s="4"/>
     </row>
     <row r="258" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A258" s="5" t="s">
-        <v>259</v>
-      </c>
-      <c r="B258" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C258" s="5" t="s">
-        <v>526</v>
-      </c>
+      <c r="A258" s="5"/>
+      <c r="B258" s="6"/>
+      <c r="C258" s="5"/>
       <c r="D258" s="4"/>
     </row>
     <row r="259" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A259" s="5" t="s">
-        <v>260</v>
-      </c>
-      <c r="B259" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C259" s="5" t="s">
-        <v>527</v>
-      </c>
+      <c r="A259" s="5"/>
+      <c r="B259" s="6"/>
+      <c r="C259" s="5"/>
       <c r="D259" s="4"/>
     </row>
     <row r="260" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A260" s="5" t="s">
-        <v>261</v>
-      </c>
-      <c r="B260" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C260" s="5" t="s">
-        <v>528</v>
-      </c>
+      <c r="A260" s="5"/>
+      <c r="B260" s="6"/>
+      <c r="C260" s="5"/>
       <c r="D260" s="4"/>
     </row>
     <row r="261" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A261" s="5" t="s">
-        <v>262</v>
-      </c>
-      <c r="B261" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C261" s="5" t="s">
-        <v>529</v>
-      </c>
+      <c r="A261" s="5"/>
+      <c r="B261" s="6"/>
+      <c r="C261" s="5"/>
       <c r="D261" s="4"/>
     </row>
     <row r="262" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A262" s="5" t="s">
-        <v>263</v>
-      </c>
-      <c r="B262" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C262" s="5" t="s">
-        <v>530</v>
-      </c>
+      <c r="A262" s="5"/>
+      <c r="B262" s="6"/>
+      <c r="C262" s="5"/>
       <c r="D262" s="4"/>
     </row>
     <row r="263" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A263" s="5" t="s">
-        <v>264</v>
-      </c>
-      <c r="B263" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C263" s="5" t="s">
-        <v>531</v>
-      </c>
+      <c r="A263" s="5"/>
+      <c r="B263" s="6"/>
+      <c r="C263" s="5"/>
       <c r="D263" s="4"/>
     </row>
     <row r="264" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A264" s="5" t="s">
-        <v>265</v>
-      </c>
-      <c r="B264" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C264" s="5" t="s">
-        <v>532</v>
-      </c>
+      <c r="A264" s="5"/>
+      <c r="B264" s="6"/>
+      <c r="C264" s="5"/>
       <c r="D264" s="4"/>
     </row>
     <row r="265" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A265" s="5" t="s">
-        <v>266</v>
-      </c>
-      <c r="B265" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C265" s="5" t="s">
-        <v>533</v>
-      </c>
+      <c r="A265" s="5"/>
+      <c r="B265" s="6"/>
+      <c r="C265" s="5"/>
       <c r="D265" s="4"/>
     </row>
     <row r="266" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A266" s="5" t="s">
-        <v>267</v>
-      </c>
-      <c r="B266" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C266" s="5" t="s">
-        <v>534</v>
-      </c>
+      <c r="A266" s="5"/>
+      <c r="B266" s="6"/>
+      <c r="C266" s="5"/>
       <c r="D266" s="4"/>
     </row>
     <row r="267" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A267" s="5" t="s">
-        <v>268</v>
-      </c>
-      <c r="B267" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C267" s="5" t="s">
-        <v>535</v>
-      </c>
+      <c r="A267" s="5"/>
+      <c r="B267" s="6"/>
+      <c r="C267" s="5"/>
       <c r="D267" s="4"/>
     </row>
     <row r="268" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A268" s="5" t="s">
-        <v>269</v>
-      </c>
-      <c r="B268" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C268" s="5" t="s">
-        <v>536</v>
-      </c>
+      <c r="A268" s="5"/>
+      <c r="B268" s="6"/>
+      <c r="C268" s="5"/>
       <c r="D268" s="4"/>
     </row>
     <row r="269" spans="1:4" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A269" s="5" t="s">
-        <v>270</v>
-      </c>
-      <c r="B269" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C269" s="5" t="s">
-        <v>537</v>
-      </c>
+      <c r="A269" s="5"/>
+      <c r="B269" s="6"/>
+      <c r="C269" s="5"/>
       <c r="D269" s="4"/>
     </row>
     <row r="270" spans="1:4" x14ac:dyDescent="0.25">
